--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksuga\.gemini\antigravity\scratch\create-timetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CCA844-B3B3-4219-B699-CA7460E8B5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2EC5E0-5CD6-4B16-A82B-48AC54730352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F317536C-8130-47EB-BB07-191DD2A1D9B2}"/>
   </bookViews>
@@ -5338,22 +5338,126 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="246" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="242" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="22" fillId="0" borderId="233" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="234" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="235" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="236" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="237" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="233" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="232" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5401,126 +5505,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="242" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="261" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="262" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="21" fillId="0" borderId="241" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="22" fillId="0" borderId="233" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="234" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="235" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="236" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="237" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="233" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="232" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="260" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="261" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="262" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6873,53 +6873,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:90" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="450"/>
-      <c r="B1" s="450"/>
-      <c r="C1" s="450"/>
-      <c r="D1" s="450"/>
-      <c r="E1" s="451" t="str">
+      <c r="A1" s="434"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="435" t="str">
         <f>_xlfn.CONCAT("【週案",AN1,"】　",TEXT(AO1,"[$-ja-JP]ge.m.d")," ～ ",TEXT(AP1,"[$-ja-JP]ge.m.d"))</f>
         <v>【週案】　M33.1.0 ～ M33.1.0</v>
       </c>
-      <c r="F1" s="451"/>
-      <c r="G1" s="451"/>
-      <c r="H1" s="451"/>
-      <c r="I1" s="451"/>
-      <c r="J1" s="451"/>
-      <c r="K1" s="451"/>
-      <c r="L1" s="451"/>
-      <c r="M1" s="451"/>
-      <c r="N1" s="451"/>
-      <c r="O1" s="451"/>
-      <c r="P1" s="451"/>
-      <c r="Q1" s="451"/>
-      <c r="R1" s="451"/>
-      <c r="S1" s="451"/>
-      <c r="T1" s="451"/>
-      <c r="U1" s="451"/>
-      <c r="V1" s="451"/>
-      <c r="W1" s="451"/>
-      <c r="X1" s="451"/>
-      <c r="Y1" s="453" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z1" s="433">
+      <c r="F1" s="435"/>
+      <c r="G1" s="435"/>
+      <c r="H1" s="435"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
+      <c r="K1" s="435"/>
+      <c r="L1" s="435"/>
+      <c r="M1" s="435"/>
+      <c r="N1" s="435"/>
+      <c r="O1" s="435"/>
+      <c r="P1" s="435"/>
+      <c r="Q1" s="435"/>
+      <c r="R1" s="435"/>
+      <c r="S1" s="435"/>
+      <c r="T1" s="435"/>
+      <c r="U1" s="435"/>
+      <c r="V1" s="435"/>
+      <c r="W1" s="435"/>
+      <c r="X1" s="435"/>
+      <c r="Y1" s="437" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="417">
         <v>1</v>
       </c>
-      <c r="AA1" s="455" t="s">
+      <c r="AA1" s="439" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="433" t="s">
+      <c r="AB1" s="417" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="433"/>
-      <c r="AD1" s="433"/>
-      <c r="AE1" s="433"/>
-      <c r="AF1" s="435">
+      <c r="AC1" s="417"/>
+      <c r="AD1" s="417"/>
+      <c r="AE1" s="417"/>
+      <c r="AF1" s="419">
         <f ca="1">NOW()</f>
-        <v>46190.967849189816</v>
-      </c>
-      <c r="AG1" s="435"/>
+        <v>46191.0062755787</v>
+      </c>
+      <c r="AG1" s="419"/>
       <c r="AH1" s="376"/>
       <c r="AI1" s="376"/>
       <c r="AJ1" s="376"/>
@@ -6927,39 +6927,39 @@
       <c r="AL1" s="376"/>
     </row>
     <row r="2" spans="1:90" ht="25.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="437"/>
-      <c r="B2" s="437"/>
-      <c r="C2" s="437"/>
-      <c r="D2" s="437"/>
-      <c r="E2" s="452"/>
-      <c r="F2" s="452"/>
-      <c r="G2" s="452"/>
-      <c r="H2" s="452"/>
-      <c r="I2" s="452"/>
-      <c r="J2" s="452"/>
-      <c r="K2" s="452"/>
-      <c r="L2" s="452"/>
-      <c r="M2" s="452"/>
-      <c r="N2" s="452"/>
-      <c r="O2" s="452"/>
-      <c r="P2" s="452"/>
-      <c r="Q2" s="452"/>
-      <c r="R2" s="452"/>
-      <c r="S2" s="452"/>
-      <c r="T2" s="452"/>
-      <c r="U2" s="452"/>
-      <c r="V2" s="452"/>
-      <c r="W2" s="452"/>
-      <c r="X2" s="452"/>
-      <c r="Y2" s="454"/>
-      <c r="Z2" s="434"/>
-      <c r="AA2" s="456"/>
-      <c r="AB2" s="434"/>
-      <c r="AC2" s="434"/>
-      <c r="AD2" s="434"/>
-      <c r="AE2" s="434"/>
-      <c r="AF2" s="436"/>
-      <c r="AG2" s="436"/>
+      <c r="A2" s="421"/>
+      <c r="B2" s="421"/>
+      <c r="C2" s="421"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="436"/>
+      <c r="F2" s="436"/>
+      <c r="G2" s="436"/>
+      <c r="H2" s="436"/>
+      <c r="I2" s="436"/>
+      <c r="J2" s="436"/>
+      <c r="K2" s="436"/>
+      <c r="L2" s="436"/>
+      <c r="M2" s="436"/>
+      <c r="N2" s="436"/>
+      <c r="O2" s="436"/>
+      <c r="P2" s="436"/>
+      <c r="Q2" s="436"/>
+      <c r="R2" s="436"/>
+      <c r="S2" s="436"/>
+      <c r="T2" s="436"/>
+      <c r="U2" s="436"/>
+      <c r="V2" s="436"/>
+      <c r="W2" s="436"/>
+      <c r="X2" s="436"/>
+      <c r="Y2" s="438"/>
+      <c r="Z2" s="418"/>
+      <c r="AA2" s="440"/>
+      <c r="AB2" s="418"/>
+      <c r="AC2" s="418"/>
+      <c r="AD2" s="418"/>
+      <c r="AE2" s="418"/>
+      <c r="AF2" s="420"/>
+      <c r="AG2" s="420"/>
       <c r="AH2" s="376"/>
       <c r="AI2" s="376"/>
       <c r="AJ2" s="376"/>
@@ -6967,86 +6967,86 @@
       <c r="AL2" s="376"/>
     </row>
     <row r="3" spans="1:90" s="2" customFormat="1" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="438"/>
-      <c r="B3" s="439"/>
-      <c r="C3" s="442"/>
-      <c r="D3" s="443"/>
-      <c r="E3" s="446">
-        <f>AO1</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="446"/>
-      <c r="G3" s="446"/>
-      <c r="H3" s="446"/>
-      <c r="I3" s="446"/>
-      <c r="J3" s="446"/>
-      <c r="K3" s="447">
-        <f>E3+1</f>
-        <v>1</v>
-      </c>
-      <c r="L3" s="448"/>
-      <c r="M3" s="448"/>
-      <c r="N3" s="448"/>
-      <c r="O3" s="448"/>
-      <c r="P3" s="449"/>
-      <c r="Q3" s="447">
-        <f>K3+1</f>
-        <v>2</v>
-      </c>
-      <c r="R3" s="448"/>
-      <c r="S3" s="448"/>
-      <c r="T3" s="448"/>
-      <c r="U3" s="449"/>
-      <c r="V3" s="447">
-        <f>Q3+1</f>
-        <v>3</v>
-      </c>
-      <c r="W3" s="448"/>
-      <c r="X3" s="448"/>
-      <c r="Y3" s="448"/>
-      <c r="Z3" s="448"/>
-      <c r="AA3" s="448"/>
-      <c r="AB3" s="447">
-        <f>V3+1</f>
-        <v>4</v>
-      </c>
-      <c r="AC3" s="448"/>
-      <c r="AD3" s="448"/>
-      <c r="AE3" s="448"/>
-      <c r="AF3" s="448"/>
-      <c r="AG3" s="449"/>
-      <c r="AH3" s="431">
-        <f>AB3+1</f>
-        <v>5</v>
-      </c>
-      <c r="AI3" s="431"/>
-      <c r="AJ3" s="431"/>
-      <c r="AK3" s="432"/>
-      <c r="AN3" s="457" t="s">
+      <c r="A3" s="422"/>
+      <c r="B3" s="423"/>
+      <c r="C3" s="426"/>
+      <c r="D3" s="427"/>
+      <c r="E3" s="430" t="str">
+        <f>TEXT(AO1,"m月d日（aaa）")</f>
+        <v>1月0日(土)</v>
+      </c>
+      <c r="F3" s="430"/>
+      <c r="G3" s="430"/>
+      <c r="H3" s="430"/>
+      <c r="I3" s="430"/>
+      <c r="J3" s="430"/>
+      <c r="K3" s="431" t="str">
+        <f>TEXT(AO1+1,"m月d日（aaa）")</f>
+        <v>1月1日(日)</v>
+      </c>
+      <c r="L3" s="432"/>
+      <c r="M3" s="432"/>
+      <c r="N3" s="432"/>
+      <c r="O3" s="432"/>
+      <c r="P3" s="433"/>
+      <c r="Q3" s="431" t="str">
+        <f>TEXT(AO1+2,"m月d日（aaa）")</f>
+        <v>1月2日(月)</v>
+      </c>
+      <c r="R3" s="432"/>
+      <c r="S3" s="432"/>
+      <c r="T3" s="432"/>
+      <c r="U3" s="433"/>
+      <c r="V3" s="431" t="str">
+        <f>TEXT(AO1+3,"m月d日（aaa）")</f>
+        <v>1月3日(火)</v>
+      </c>
+      <c r="W3" s="432"/>
+      <c r="X3" s="432"/>
+      <c r="Y3" s="432"/>
+      <c r="Z3" s="432"/>
+      <c r="AA3" s="432"/>
+      <c r="AB3" s="431" t="str">
+        <f>TEXT(AO1+4,"m月d日（aaa）")</f>
+        <v>1月4日(水)</v>
+      </c>
+      <c r="AC3" s="432"/>
+      <c r="AD3" s="432"/>
+      <c r="AE3" s="432"/>
+      <c r="AF3" s="432"/>
+      <c r="AG3" s="433"/>
+      <c r="AH3" s="444" t="str">
+        <f>TEXT(AO1+5,"m月d日（aaa）")</f>
+        <v>1月5日(木)</v>
+      </c>
+      <c r="AI3" s="444"/>
+      <c r="AJ3" s="444"/>
+      <c r="AK3" s="445"/>
+      <c r="AN3" s="466" t="s">
         <v>39</v>
       </c>
-      <c r="AO3" s="410" t="s">
+      <c r="AO3" s="462" t="s">
         <v>40</v>
       </c>
-      <c r="AP3" s="410" t="s">
+      <c r="AP3" s="462" t="s">
         <v>41</v>
       </c>
-      <c r="AQ3" s="410" t="s">
+      <c r="AQ3" s="462" t="s">
         <v>42</v>
       </c>
-      <c r="AR3" s="410" t="s">
+      <c r="AR3" s="462" t="s">
         <v>43</v>
       </c>
-      <c r="AS3" s="410" t="s">
+      <c r="AS3" s="462" t="s">
         <v>44</v>
       </c>
-      <c r="AT3" s="410" t="s">
+      <c r="AT3" s="462" t="s">
         <v>45</v>
       </c>
-      <c r="AU3" s="410" t="s">
+      <c r="AU3" s="462" t="s">
         <v>46</v>
       </c>
-      <c r="AV3" s="411" t="s">
+      <c r="AV3" s="464" t="s">
         <v>47</v>
       </c>
       <c r="BD3" s="4"/>
@@ -7085,10 +7085,10 @@
       <c r="CL3" s="4"/>
     </row>
     <row r="4" spans="1:90" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="440"/>
-      <c r="B4" s="441"/>
-      <c r="C4" s="444"/>
-      <c r="D4" s="445"/>
+      <c r="A4" s="424"/>
+      <c r="B4" s="425"/>
+      <c r="C4" s="428"/>
+      <c r="D4" s="429"/>
       <c r="E4" s="5">
         <v>1</v>
       </c>
@@ -7188,18 +7188,18 @@
       <c r="AK4" s="21">
         <v>4</v>
       </c>
-      <c r="AN4" s="465"/>
-      <c r="AO4" s="466"/>
-      <c r="AP4" s="466"/>
-      <c r="AQ4" s="466"/>
-      <c r="AR4" s="466"/>
-      <c r="AS4" s="466"/>
-      <c r="AT4" s="466"/>
-      <c r="AU4" s="466"/>
-      <c r="AV4" s="467"/>
+      <c r="AN4" s="467"/>
+      <c r="AO4" s="463"/>
+      <c r="AP4" s="463"/>
+      <c r="AQ4" s="463"/>
+      <c r="AR4" s="463"/>
+      <c r="AS4" s="463"/>
+      <c r="AT4" s="463"/>
+      <c r="AU4" s="463"/>
+      <c r="AV4" s="465"/>
     </row>
     <row r="5" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="428" t="s">
+      <c r="A5" s="441" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="22" t="s">
@@ -7300,7 +7300,7 @@
       </c>
     </row>
     <row r="6" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="429"/>
+      <c r="A6" s="442"/>
       <c r="B6" s="30" t="s">
         <v>5</v>
       </c>
@@ -7399,7 +7399,7 @@
       </c>
     </row>
     <row r="7" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="429"/>
+      <c r="A7" s="442"/>
       <c r="B7" s="30" t="s">
         <v>6</v>
       </c>
@@ -7498,7 +7498,7 @@
       </c>
     </row>
     <row r="8" spans="1:90" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="429"/>
+      <c r="A8" s="442"/>
       <c r="B8" s="30" t="s">
         <v>7</v>
       </c>
@@ -7597,7 +7597,7 @@
       </c>
     </row>
     <row r="9" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="430"/>
+      <c r="A9" s="443"/>
       <c r="B9" s="35" t="s">
         <v>8</v>
       </c>
@@ -7696,7 +7696,7 @@
       </c>
     </row>
     <row r="10" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="428" t="s">
+      <c r="A10" s="441" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -7798,7 +7798,7 @@
       </c>
     </row>
     <row r="11" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="429"/>
+      <c r="A11" s="442"/>
       <c r="B11" s="30" t="s">
         <v>5</v>
       </c>
@@ -7898,7 +7898,7 @@
       </c>
     </row>
     <row r="12" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="429"/>
+      <c r="A12" s="442"/>
       <c r="B12" s="30" t="s">
         <v>6</v>
       </c>
@@ -7998,7 +7998,7 @@
       </c>
     </row>
     <row r="13" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="429"/>
+      <c r="A13" s="442"/>
       <c r="B13" s="30" t="s">
         <v>7</v>
       </c>
@@ -8098,7 +8098,7 @@
       </c>
     </row>
     <row r="14" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="430"/>
+      <c r="A14" s="443"/>
       <c r="B14" s="35" t="s">
         <v>8</v>
       </c>
@@ -8198,7 +8198,7 @@
       </c>
     </row>
     <row r="15" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="429" t="s">
+      <c r="A15" s="442" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="22" t="s">
@@ -8300,7 +8300,7 @@
       </c>
     </row>
     <row r="16" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="429"/>
+      <c r="A16" s="442"/>
       <c r="B16" s="30" t="s">
         <v>5</v>
       </c>
@@ -8400,7 +8400,7 @@
       </c>
     </row>
     <row r="17" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="429"/>
+      <c r="A17" s="442"/>
       <c r="B17" s="30" t="s">
         <v>6</v>
       </c>
@@ -8500,7 +8500,7 @@
       </c>
     </row>
     <row r="18" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="429"/>
+      <c r="A18" s="442"/>
       <c r="B18" s="30" t="s">
         <v>7</v>
       </c>
@@ -8600,7 +8600,7 @@
       </c>
     </row>
     <row r="19" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="429"/>
+      <c r="A19" s="442"/>
       <c r="B19" s="35" t="s">
         <v>8</v>
       </c>
@@ -8698,9 +8698,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BD19" s="414"/>
-      <c r="BE19" s="415"/>
-      <c r="BF19" s="415"/>
+      <c r="BD19" s="446"/>
+      <c r="BE19" s="447"/>
+      <c r="BF19" s="447"/>
       <c r="BJ19" s="56"/>
       <c r="BK19" s="56"/>
       <c r="BL19" s="56"/>
@@ -8787,7 +8787,7 @@
       <c r="BC20" s="392"/>
     </row>
     <row r="21" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="429" t="s">
+      <c r="A21" s="442" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="68" t="s">
@@ -8903,7 +8903,7 @@
       <c r="BI21" s="81"/>
     </row>
     <row r="22" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="429"/>
+      <c r="A22" s="442"/>
       <c r="B22" s="82" t="s">
         <v>28</v>
       </c>
@@ -9017,7 +9017,7 @@
       <c r="BI22" s="81"/>
     </row>
     <row r="23" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="429"/>
+      <c r="A23" s="442"/>
       <c r="B23" s="90" t="s">
         <v>29</v>
       </c>
@@ -9131,7 +9131,7 @@
       <c r="BI23" s="81"/>
     </row>
     <row r="24" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="429"/>
+      <c r="A24" s="442"/>
       <c r="B24" s="98" t="s">
         <v>7</v>
       </c>
@@ -9245,7 +9245,7 @@
       <c r="BI24" s="81"/>
     </row>
     <row r="25" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="429"/>
+      <c r="A25" s="442"/>
       <c r="B25" s="98" t="s">
         <v>8</v>
       </c>
@@ -9359,7 +9359,7 @@
       <c r="BI25" s="81"/>
     </row>
     <row r="26" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="429"/>
+      <c r="A26" s="442"/>
       <c r="B26" s="99" t="s">
         <v>30</v>
       </c>
@@ -9473,7 +9473,7 @@
       <c r="BI26" s="81"/>
     </row>
     <row r="27" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="429"/>
+      <c r="A27" s="442"/>
       <c r="B27" s="82" t="s">
         <v>30</v>
       </c>
@@ -9587,7 +9587,7 @@
       <c r="BI27" s="81"/>
     </row>
     <row r="28" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="429"/>
+      <c r="A28" s="442"/>
       <c r="B28" s="82" t="s">
         <v>30</v>
       </c>
@@ -9701,7 +9701,7 @@
       <c r="BI28" s="81"/>
     </row>
     <row r="29" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="429"/>
+      <c r="A29" s="442"/>
       <c r="B29" s="82" t="s">
         <v>30</v>
       </c>
@@ -9815,7 +9815,7 @@
       <c r="BI29" s="81"/>
     </row>
     <row r="30" spans="1:90" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="429"/>
+      <c r="A30" s="442"/>
       <c r="B30" s="82" t="s">
         <v>30</v>
       </c>
@@ -9929,7 +9929,7 @@
       <c r="BI30" s="81"/>
     </row>
     <row r="31" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="428" t="s">
+      <c r="A31" s="441" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="115" t="s">
@@ -10045,7 +10045,7 @@
       <c r="BI31" s="81"/>
     </row>
     <row r="32" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="429"/>
+      <c r="A32" s="442"/>
       <c r="B32" s="132" t="s">
         <v>28</v>
       </c>
@@ -10159,7 +10159,7 @@
       <c r="BI32" s="81"/>
     </row>
     <row r="33" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="429"/>
+      <c r="A33" s="442"/>
       <c r="B33" s="68" t="s">
         <v>29</v>
       </c>
@@ -10273,7 +10273,7 @@
       <c r="BI33" s="81"/>
     </row>
     <row r="34" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="429"/>
+      <c r="A34" s="442"/>
       <c r="B34" s="132" t="s">
         <v>32</v>
       </c>
@@ -10387,7 +10387,7 @@
       <c r="BI34" s="81"/>
     </row>
     <row r="35" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="429"/>
+      <c r="A35" s="442"/>
       <c r="B35" s="143" t="s">
         <v>33</v>
       </c>
@@ -10501,7 +10501,7 @@
       <c r="BI35" s="81"/>
     </row>
     <row r="36" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="429"/>
+      <c r="A36" s="442"/>
       <c r="B36" s="149" t="s">
         <v>30</v>
       </c>
@@ -10615,7 +10615,7 @@
       <c r="BI36" s="81"/>
     </row>
     <row r="37" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="429"/>
+      <c r="A37" s="442"/>
       <c r="B37" s="82" t="s">
         <v>30</v>
       </c>
@@ -10729,7 +10729,7 @@
       <c r="BI37" s="81"/>
     </row>
     <row r="38" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="429"/>
+      <c r="A38" s="442"/>
       <c r="B38" s="154" t="s">
         <v>30</v>
       </c>
@@ -10843,7 +10843,7 @@
       <c r="BI38" s="81"/>
     </row>
     <row r="39" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="429"/>
+      <c r="A39" s="442"/>
       <c r="B39" s="154" t="s">
         <v>30</v>
       </c>
@@ -10957,7 +10957,7 @@
       <c r="BI39" s="81"/>
     </row>
     <row r="40" spans="1:61" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="430"/>
+      <c r="A40" s="443"/>
       <c r="B40" s="165" t="s">
         <v>30</v>
       </c>
@@ -11071,7 +11071,7 @@
       <c r="BI40" s="81"/>
     </row>
     <row r="41" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="428" t="s">
+      <c r="A41" s="441" t="s">
         <v>34</v>
       </c>
       <c r="B41" s="169" t="s">
@@ -11187,7 +11187,7 @@
       <c r="BI41" s="81"/>
     </row>
     <row r="42" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="429"/>
+      <c r="A42" s="442"/>
       <c r="B42" s="170" t="s">
         <v>28</v>
       </c>
@@ -11301,7 +11301,7 @@
       <c r="BI42" s="81"/>
     </row>
     <row r="43" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="429"/>
+      <c r="A43" s="442"/>
       <c r="B43" s="181" t="s">
         <v>29</v>
       </c>
@@ -11415,7 +11415,7 @@
       <c r="BI43" s="81"/>
     </row>
     <row r="44" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="429"/>
+      <c r="A44" s="442"/>
       <c r="B44" s="182" t="s">
         <v>32</v>
       </c>
@@ -11529,7 +11529,7 @@
       <c r="BI44" s="81"/>
     </row>
     <row r="45" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="429"/>
+      <c r="A45" s="442"/>
       <c r="B45" s="187" t="s">
         <v>33</v>
       </c>
@@ -11643,7 +11643,7 @@
       <c r="BI45" s="81"/>
     </row>
     <row r="46" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="429"/>
+      <c r="A46" s="442"/>
       <c r="B46" s="194" t="s">
         <v>30</v>
       </c>
@@ -11757,7 +11757,7 @@
       <c r="BI46" s="81"/>
     </row>
     <row r="47" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="429"/>
+      <c r="A47" s="442"/>
       <c r="B47" s="195" t="s">
         <v>30</v>
       </c>
@@ -11871,7 +11871,7 @@
       <c r="BI47" s="81"/>
     </row>
     <row r="48" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="429"/>
+      <c r="A48" s="442"/>
       <c r="B48" s="195" t="s">
         <v>30</v>
       </c>
@@ -11985,7 +11985,7 @@
       <c r="BI48" s="81"/>
     </row>
     <row r="49" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="429"/>
+      <c r="A49" s="442"/>
       <c r="B49" s="195" t="s">
         <v>30</v>
       </c>
@@ -12099,7 +12099,7 @@
       <c r="BI49" s="81"/>
     </row>
     <row r="50" spans="1:61" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="430"/>
+      <c r="A50" s="443"/>
       <c r="B50" s="205" t="s">
         <v>30</v>
       </c>
@@ -12213,7 +12213,7 @@
       <c r="BI50" s="81"/>
     </row>
     <row r="51" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="428" t="s">
+      <c r="A51" s="441" t="s">
         <v>35</v>
       </c>
       <c r="B51" s="220" t="s">
@@ -12329,7 +12329,7 @@
       <c r="BI51" s="81"/>
     </row>
     <row r="52" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="429"/>
+      <c r="A52" s="442"/>
       <c r="B52" s="230" t="s">
         <v>36</v>
       </c>
@@ -12443,7 +12443,7 @@
       <c r="BI52" s="81"/>
     </row>
     <row r="53" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="429"/>
+      <c r="A53" s="442"/>
       <c r="B53" s="230" t="s">
         <v>36</v>
       </c>
@@ -12557,7 +12557,7 @@
       <c r="BI53" s="81"/>
     </row>
     <row r="54" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="429"/>
+      <c r="A54" s="442"/>
       <c r="B54" s="230" t="s">
         <v>36</v>
       </c>
@@ -12671,7 +12671,7 @@
       <c r="BI54" s="81"/>
     </row>
     <row r="55" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="429"/>
+      <c r="A55" s="442"/>
       <c r="B55" s="230" t="s">
         <v>36</v>
       </c>
@@ -12785,7 +12785,7 @@
       <c r="BI55" s="81"/>
     </row>
     <row r="56" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="429"/>
+      <c r="A56" s="442"/>
       <c r="B56" s="230" t="s">
         <v>36</v>
       </c>
@@ -12899,7 +12899,7 @@
       <c r="BI56" s="81"/>
     </row>
     <row r="57" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="429"/>
+      <c r="A57" s="442"/>
       <c r="B57" s="230" t="s">
         <v>36</v>
       </c>
@@ -13013,7 +13013,7 @@
       <c r="BI57" s="81"/>
     </row>
     <row r="58" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="429"/>
+      <c r="A58" s="442"/>
       <c r="B58" s="230" t="s">
         <v>36</v>
       </c>
@@ -13127,7 +13127,7 @@
       <c r="BI58" s="81"/>
     </row>
     <row r="59" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="429"/>
+      <c r="A59" s="442"/>
       <c r="B59" s="230" t="s">
         <v>36</v>
       </c>
@@ -13241,7 +13241,7 @@
       <c r="BI59" s="81"/>
     </row>
     <row r="60" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="429"/>
+      <c r="A60" s="442"/>
       <c r="B60" s="230" t="s">
         <v>36</v>
       </c>
@@ -13355,7 +13355,7 @@
       <c r="BI60" s="81"/>
     </row>
     <row r="61" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="429"/>
+      <c r="A61" s="442"/>
       <c r="B61" s="230" t="s">
         <v>36</v>
       </c>
@@ -13469,7 +13469,7 @@
       <c r="BI61" s="81"/>
     </row>
     <row r="62" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="429"/>
+      <c r="A62" s="442"/>
       <c r="B62" s="230" t="s">
         <v>36</v>
       </c>
@@ -13583,7 +13583,7 @@
       <c r="BI62" s="81"/>
     </row>
     <row r="63" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="429"/>
+      <c r="A63" s="442"/>
       <c r="B63" s="230" t="s">
         <v>36</v>
       </c>
@@ -13697,7 +13697,7 @@
       <c r="BI63" s="81"/>
     </row>
     <row r="64" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="429"/>
+      <c r="A64" s="442"/>
       <c r="B64" s="230" t="s">
         <v>36</v>
       </c>
@@ -13811,7 +13811,7 @@
       <c r="BI64" s="81"/>
     </row>
     <row r="65" spans="1:90" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="430"/>
+      <c r="A65" s="443"/>
       <c r="B65" s="238" t="s">
         <v>36</v>
       </c>
@@ -13925,91 +13925,91 @@
       <c r="BI65" s="81"/>
     </row>
     <row r="66" spans="1:90" s="246" customFormat="1" ht="52.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="416"/>
-      <c r="B66" s="417"/>
-      <c r="C66" s="417"/>
-      <c r="D66" s="418"/>
-      <c r="E66" s="419"/>
-      <c r="F66" s="420"/>
-      <c r="G66" s="420"/>
-      <c r="H66" s="420"/>
-      <c r="I66" s="420"/>
-      <c r="J66" s="421"/>
-      <c r="K66" s="422"/>
-      <c r="L66" s="423"/>
-      <c r="M66" s="423"/>
-      <c r="N66" s="423"/>
-      <c r="O66" s="423"/>
-      <c r="P66" s="424"/>
-      <c r="Q66" s="422"/>
-      <c r="R66" s="423"/>
-      <c r="S66" s="423"/>
-      <c r="T66" s="423"/>
-      <c r="U66" s="424"/>
-      <c r="V66" s="422"/>
-      <c r="W66" s="423"/>
-      <c r="X66" s="423"/>
-      <c r="Y66" s="423"/>
-      <c r="Z66" s="423"/>
-      <c r="AA66" s="424"/>
-      <c r="AB66" s="422"/>
-      <c r="AC66" s="423"/>
-      <c r="AD66" s="423"/>
-      <c r="AE66" s="423"/>
-      <c r="AF66" s="423"/>
-      <c r="AG66" s="424"/>
-      <c r="AH66" s="425" t="e">
+      <c r="A66" s="450"/>
+      <c r="B66" s="451"/>
+      <c r="C66" s="451"/>
+      <c r="D66" s="452"/>
+      <c r="E66" s="453"/>
+      <c r="F66" s="454"/>
+      <c r="G66" s="454"/>
+      <c r="H66" s="454"/>
+      <c r="I66" s="454"/>
+      <c r="J66" s="455"/>
+      <c r="K66" s="456"/>
+      <c r="L66" s="457"/>
+      <c r="M66" s="457"/>
+      <c r="N66" s="457"/>
+      <c r="O66" s="457"/>
+      <c r="P66" s="458"/>
+      <c r="Q66" s="456"/>
+      <c r="R66" s="457"/>
+      <c r="S66" s="457"/>
+      <c r="T66" s="457"/>
+      <c r="U66" s="458"/>
+      <c r="V66" s="456"/>
+      <c r="W66" s="457"/>
+      <c r="X66" s="457"/>
+      <c r="Y66" s="457"/>
+      <c r="Z66" s="457"/>
+      <c r="AA66" s="458"/>
+      <c r="AB66" s="456"/>
+      <c r="AC66" s="457"/>
+      <c r="AD66" s="457"/>
+      <c r="AE66" s="457"/>
+      <c r="AF66" s="457"/>
+      <c r="AG66" s="458"/>
+      <c r="AH66" s="459" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI66" s="426"/>
-      <c r="AJ66" s="426"/>
-      <c r="AK66" s="427"/>
-      <c r="AN66" s="458" t="s">
+      <c r="AI66" s="460"/>
+      <c r="AJ66" s="460"/>
+      <c r="AK66" s="461"/>
+      <c r="AN66" s="410" t="s">
         <v>11</v>
       </c>
-      <c r="AO66" s="459" t="s">
+      <c r="AO66" s="411" t="s">
         <v>12</v>
       </c>
-      <c r="AP66" s="460" t="s">
+      <c r="AP66" s="412" t="s">
         <v>13</v>
       </c>
-      <c r="AQ66" s="461" t="s">
+      <c r="AQ66" s="413" t="s">
         <v>14</v>
       </c>
-      <c r="AR66" s="460" t="s">
+      <c r="AR66" s="412" t="s">
         <v>15</v>
       </c>
-      <c r="AS66" s="461" t="s">
+      <c r="AS66" s="413" t="s">
         <v>16</v>
       </c>
-      <c r="AT66" s="459" t="s">
+      <c r="AT66" s="411" t="s">
         <v>17</v>
       </c>
-      <c r="AU66" s="459" t="s">
+      <c r="AU66" s="411" t="s">
         <v>18</v>
       </c>
-      <c r="AV66" s="459" t="s">
+      <c r="AV66" s="411" t="s">
         <v>19</v>
       </c>
-      <c r="AW66" s="460" t="s">
+      <c r="AW66" s="412" t="s">
         <v>20</v>
       </c>
-      <c r="AX66" s="461" t="s">
+      <c r="AX66" s="413" t="s">
         <v>21</v>
       </c>
-      <c r="AY66" s="459" t="s">
+      <c r="AY66" s="411" t="s">
         <v>22</v>
       </c>
-      <c r="AZ66" s="462" t="s">
+      <c r="AZ66" s="414" t="s">
         <v>23</v>
       </c>
-      <c r="BA66" s="463" t="s">
+      <c r="BA66" s="415" t="s">
         <v>24</v>
       </c>
-      <c r="BB66" s="462" t="s">
+      <c r="BB66" s="414" t="s">
         <v>25</v>
       </c>
-      <c r="BC66" s="464" t="s">
+      <c r="BC66" s="416" t="s">
         <v>26</v>
       </c>
       <c r="BD66" s="247"/>
@@ -14051,10 +14051,10 @@
       </c>
     </row>
     <row r="77" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C77" s="412" t="s">
+      <c r="C77" s="448" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="413"/>
+      <c r="D77" s="449"/>
       <c r="E77" s="1">
         <f>COUNTIF(E$21:E$65,"*"&amp;$C77&amp;"*")</f>
         <v>0</v>
@@ -14189,10 +14189,10 @@
       </c>
     </row>
     <row r="78" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C78" s="412" t="s">
+      <c r="C78" s="448" t="s">
         <v>49</v>
       </c>
-      <c r="D78" s="413"/>
+      <c r="D78" s="449"/>
       <c r="E78" s="1">
         <f t="shared" ref="E78:T96" si="14">COUNTIF(E$21:E$65,"*"&amp;$C78&amp;"*")</f>
         <v>0</v>
@@ -14327,10 +14327,10 @@
       </c>
     </row>
     <row r="79" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C79" s="412" t="s">
+      <c r="C79" s="448" t="s">
         <v>50</v>
       </c>
-      <c r="D79" s="413"/>
+      <c r="D79" s="449"/>
       <c r="E79" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14465,10 +14465,10 @@
       </c>
     </row>
     <row r="80" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C80" s="412" t="s">
+      <c r="C80" s="448" t="s">
         <v>51</v>
       </c>
-      <c r="D80" s="413"/>
+      <c r="D80" s="449"/>
       <c r="E80" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14603,10 +14603,10 @@
       </c>
     </row>
     <row r="81" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C81" s="412" t="s">
+      <c r="C81" s="448" t="s">
         <v>17</v>
       </c>
-      <c r="D81" s="413"/>
+      <c r="D81" s="449"/>
       <c r="E81" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14741,10 +14741,10 @@
       </c>
     </row>
     <row r="82" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C82" s="412" t="s">
+      <c r="C82" s="448" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="413"/>
+      <c r="D82" s="449"/>
       <c r="E82" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14879,10 +14879,10 @@
       </c>
     </row>
     <row r="83" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C83" s="412" t="s">
+      <c r="C83" s="448" t="s">
         <v>52</v>
       </c>
-      <c r="D83" s="413"/>
+      <c r="D83" s="449"/>
       <c r="E83" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15017,10 +15017,10 @@
       </c>
     </row>
     <row r="84" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C84" s="412" t="s">
+      <c r="C84" s="448" t="s">
         <v>22</v>
       </c>
-      <c r="D84" s="413"/>
+      <c r="D84" s="449"/>
       <c r="E84" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15155,10 +15155,10 @@
       </c>
     </row>
     <row r="85" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C85" s="412" t="s">
+      <c r="C85" s="448" t="s">
         <v>23</v>
       </c>
-      <c r="D85" s="413"/>
+      <c r="D85" s="449"/>
       <c r="E85" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15293,10 +15293,10 @@
       </c>
     </row>
     <row r="86" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C86" s="412" t="s">
+      <c r="C86" s="448" t="s">
         <v>53</v>
       </c>
-      <c r="D86" s="413"/>
+      <c r="D86" s="449"/>
       <c r="E86" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15431,10 +15431,10 @@
       </c>
     </row>
     <row r="87" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C87" s="412" t="s">
+      <c r="C87" s="448" t="s">
         <v>54</v>
       </c>
-      <c r="D87" s="413"/>
+      <c r="D87" s="449"/>
       <c r="E87" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15569,10 +15569,10 @@
       </c>
     </row>
     <row r="88" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C88" s="412" t="s">
+      <c r="C88" s="448" t="s">
         <v>55</v>
       </c>
-      <c r="D88" s="413"/>
+      <c r="D88" s="449"/>
       <c r="E88" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15707,10 +15707,10 @@
       </c>
     </row>
     <row r="89" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C89" s="412" t="s">
+      <c r="C89" s="448" t="s">
         <v>56</v>
       </c>
-      <c r="D89" s="413"/>
+      <c r="D89" s="449"/>
       <c r="E89" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15845,10 +15845,10 @@
       </c>
     </row>
     <row r="90" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C90" s="412" t="s">
+      <c r="C90" s="448" t="s">
         <v>57</v>
       </c>
-      <c r="D90" s="413"/>
+      <c r="D90" s="449"/>
       <c r="E90" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15983,10 +15983,10 @@
       </c>
     </row>
     <row r="91" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C91" s="412" t="s">
+      <c r="C91" s="448" t="s">
         <v>58</v>
       </c>
-      <c r="D91" s="413"/>
+      <c r="D91" s="449"/>
       <c r="E91" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16121,10 +16121,10 @@
       </c>
     </row>
     <row r="92" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C92" s="412">
-        <v>0</v>
-      </c>
-      <c r="D92" s="413"/>
+      <c r="C92" s="448">
+        <v>0</v>
+      </c>
+      <c r="D92" s="449"/>
       <c r="E92" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16259,10 +16259,10 @@
       </c>
     </row>
     <row r="93" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C93" s="412">
-        <v>0</v>
-      </c>
-      <c r="D93" s="413"/>
+      <c r="C93" s="448">
+        <v>0</v>
+      </c>
+      <c r="D93" s="449"/>
       <c r="E93" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16397,10 +16397,10 @@
       </c>
     </row>
     <row r="94" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C94" s="412">
-        <v>0</v>
-      </c>
-      <c r="D94" s="413"/>
+      <c r="C94" s="448">
+        <v>0</v>
+      </c>
+      <c r="D94" s="449"/>
       <c r="E94" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16535,10 +16535,10 @@
       </c>
     </row>
     <row r="95" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C95" s="412">
-        <v>0</v>
-      </c>
-      <c r="D95" s="413"/>
+      <c r="C95" s="448">
+        <v>0</v>
+      </c>
+      <c r="D95" s="449"/>
       <c r="E95" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16673,10 +16673,10 @@
       </c>
     </row>
     <row r="96" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C96" s="412">
-        <v>0</v>
-      </c>
-      <c r="D96" s="413"/>
+      <c r="C96" s="448">
+        <v>0</v>
+      </c>
+      <c r="D96" s="449"/>
       <c r="E96" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -25108,26 +25108,30 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="60">
-    <mergeCell ref="AB1:AE2"/>
-    <mergeCell ref="AF1:AG2"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="V3:AA3"/>
-    <mergeCell ref="AB3:AG3"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="A41:A50"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AU3:AU4"/>
+    <mergeCell ref="AV3:AV4"/>
+    <mergeCell ref="AR3:AR4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AP3:AP4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="AS3:AS4"/>
+    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C87:D87"/>
     <mergeCell ref="BD19:BF19"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A66:D66"/>
@@ -25144,30 +25148,26 @@
     <mergeCell ref="A51:A65"/>
     <mergeCell ref="A21:A30"/>
     <mergeCell ref="A31:A40"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="AU3:AU4"/>
-    <mergeCell ref="AV3:AV4"/>
-    <mergeCell ref="AR3:AR4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AS3:AS4"/>
-    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="A41:A50"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AB1:AE2"/>
+    <mergeCell ref="AF1:AG2"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:X2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="AA1:AA2"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C5:D19">

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksuga\.gemini\antigravity\scratch\create-timetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2EC5E0-5CD6-4B16-A82B-48AC54730352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856F6C18-294E-480E-A318-05A14C156786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F317536C-8130-47EB-BB07-191DD2A1D9B2}"/>
   </bookViews>
@@ -5359,6 +5359,96 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="232" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="242" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="261" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="262" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="241" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="260" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -5432,96 +5522,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="242" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="261" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="262" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="241" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="260" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6873,53 +6873,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:90" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="434"/>
-      <c r="B1" s="434"/>
-      <c r="C1" s="434"/>
-      <c r="D1" s="434"/>
-      <c r="E1" s="435" t="str">
+      <c r="A1" s="461"/>
+      <c r="B1" s="461"/>
+      <c r="C1" s="461"/>
+      <c r="D1" s="461"/>
+      <c r="E1" s="462" t="str">
         <f>_xlfn.CONCAT("【週案",AN1,"】　",TEXT(AO1,"[$-ja-JP]ge.m.d")," ～ ",TEXT(AP1,"[$-ja-JP]ge.m.d"))</f>
         <v>【週案】　M33.1.0 ～ M33.1.0</v>
       </c>
-      <c r="F1" s="435"/>
-      <c r="G1" s="435"/>
-      <c r="H1" s="435"/>
-      <c r="I1" s="435"/>
-      <c r="J1" s="435"/>
-      <c r="K1" s="435"/>
-      <c r="L1" s="435"/>
-      <c r="M1" s="435"/>
-      <c r="N1" s="435"/>
-      <c r="O1" s="435"/>
-      <c r="P1" s="435"/>
-      <c r="Q1" s="435"/>
-      <c r="R1" s="435"/>
-      <c r="S1" s="435"/>
-      <c r="T1" s="435"/>
-      <c r="U1" s="435"/>
-      <c r="V1" s="435"/>
-      <c r="W1" s="435"/>
-      <c r="X1" s="435"/>
-      <c r="Y1" s="437" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z1" s="417">
+      <c r="F1" s="462"/>
+      <c r="G1" s="462"/>
+      <c r="H1" s="462"/>
+      <c r="I1" s="462"/>
+      <c r="J1" s="462"/>
+      <c r="K1" s="462"/>
+      <c r="L1" s="462"/>
+      <c r="M1" s="462"/>
+      <c r="N1" s="462"/>
+      <c r="O1" s="462"/>
+      <c r="P1" s="462"/>
+      <c r="Q1" s="462"/>
+      <c r="R1" s="462"/>
+      <c r="S1" s="462"/>
+      <c r="T1" s="462"/>
+      <c r="U1" s="462"/>
+      <c r="V1" s="462"/>
+      <c r="W1" s="462"/>
+      <c r="X1" s="462"/>
+      <c r="Y1" s="464" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="444">
         <v>1</v>
       </c>
-      <c r="AA1" s="439" t="s">
+      <c r="AA1" s="466" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="417" t="s">
+      <c r="AB1" s="444" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="417"/>
-      <c r="AD1" s="417"/>
-      <c r="AE1" s="417"/>
-      <c r="AF1" s="419">
+      <c r="AC1" s="444"/>
+      <c r="AD1" s="444"/>
+      <c r="AE1" s="444"/>
+      <c r="AF1" s="446">
         <f ca="1">NOW()</f>
-        <v>46191.0062755787</v>
-      </c>
-      <c r="AG1" s="419"/>
+        <v>46191.035811458336</v>
+      </c>
+      <c r="AG1" s="446"/>
       <c r="AH1" s="376"/>
       <c r="AI1" s="376"/>
       <c r="AJ1" s="376"/>
@@ -6927,39 +6927,39 @@
       <c r="AL1" s="376"/>
     </row>
     <row r="2" spans="1:90" ht="25.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="421"/>
-      <c r="B2" s="421"/>
-      <c r="C2" s="421"/>
-      <c r="D2" s="421"/>
-      <c r="E2" s="436"/>
-      <c r="F2" s="436"/>
-      <c r="G2" s="436"/>
-      <c r="H2" s="436"/>
-      <c r="I2" s="436"/>
-      <c r="J2" s="436"/>
-      <c r="K2" s="436"/>
-      <c r="L2" s="436"/>
-      <c r="M2" s="436"/>
-      <c r="N2" s="436"/>
-      <c r="O2" s="436"/>
-      <c r="P2" s="436"/>
-      <c r="Q2" s="436"/>
-      <c r="R2" s="436"/>
-      <c r="S2" s="436"/>
-      <c r="T2" s="436"/>
-      <c r="U2" s="436"/>
-      <c r="V2" s="436"/>
-      <c r="W2" s="436"/>
-      <c r="X2" s="436"/>
-      <c r="Y2" s="438"/>
-      <c r="Z2" s="418"/>
-      <c r="AA2" s="440"/>
-      <c r="AB2" s="418"/>
-      <c r="AC2" s="418"/>
-      <c r="AD2" s="418"/>
-      <c r="AE2" s="418"/>
-      <c r="AF2" s="420"/>
-      <c r="AG2" s="420"/>
+      <c r="A2" s="448"/>
+      <c r="B2" s="448"/>
+      <c r="C2" s="448"/>
+      <c r="D2" s="448"/>
+      <c r="E2" s="463"/>
+      <c r="F2" s="463"/>
+      <c r="G2" s="463"/>
+      <c r="H2" s="463"/>
+      <c r="I2" s="463"/>
+      <c r="J2" s="463"/>
+      <c r="K2" s="463"/>
+      <c r="L2" s="463"/>
+      <c r="M2" s="463"/>
+      <c r="N2" s="463"/>
+      <c r="O2" s="463"/>
+      <c r="P2" s="463"/>
+      <c r="Q2" s="463"/>
+      <c r="R2" s="463"/>
+      <c r="S2" s="463"/>
+      <c r="T2" s="463"/>
+      <c r="U2" s="463"/>
+      <c r="V2" s="463"/>
+      <c r="W2" s="463"/>
+      <c r="X2" s="463"/>
+      <c r="Y2" s="465"/>
+      <c r="Z2" s="445"/>
+      <c r="AA2" s="467"/>
+      <c r="AB2" s="445"/>
+      <c r="AC2" s="445"/>
+      <c r="AD2" s="445"/>
+      <c r="AE2" s="445"/>
+      <c r="AF2" s="447"/>
+      <c r="AG2" s="447"/>
       <c r="AH2" s="376"/>
       <c r="AI2" s="376"/>
       <c r="AJ2" s="376"/>
@@ -6967,86 +6967,86 @@
       <c r="AL2" s="376"/>
     </row>
     <row r="3" spans="1:90" s="2" customFormat="1" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="422"/>
-      <c r="B3" s="423"/>
-      <c r="C3" s="426"/>
-      <c r="D3" s="427"/>
-      <c r="E3" s="430" t="str">
+      <c r="A3" s="449"/>
+      <c r="B3" s="450"/>
+      <c r="C3" s="453"/>
+      <c r="D3" s="454"/>
+      <c r="E3" s="457" t="str">
         <f>TEXT(AO1,"m月d日（aaa）")</f>
         <v>1月0日(土)</v>
       </c>
-      <c r="F3" s="430"/>
-      <c r="G3" s="430"/>
-      <c r="H3" s="430"/>
-      <c r="I3" s="430"/>
-      <c r="J3" s="430"/>
-      <c r="K3" s="431" t="str">
+      <c r="F3" s="457"/>
+      <c r="G3" s="457"/>
+      <c r="H3" s="457"/>
+      <c r="I3" s="457"/>
+      <c r="J3" s="457"/>
+      <c r="K3" s="458" t="str">
         <f>TEXT(AO1+1,"m月d日（aaa）")</f>
         <v>1月1日(日)</v>
       </c>
-      <c r="L3" s="432"/>
-      <c r="M3" s="432"/>
-      <c r="N3" s="432"/>
-      <c r="O3" s="432"/>
-      <c r="P3" s="433"/>
-      <c r="Q3" s="431" t="str">
+      <c r="L3" s="459"/>
+      <c r="M3" s="459"/>
+      <c r="N3" s="459"/>
+      <c r="O3" s="459"/>
+      <c r="P3" s="460"/>
+      <c r="Q3" s="458" t="str">
         <f>TEXT(AO1+2,"m月d日（aaa）")</f>
         <v>1月2日(月)</v>
       </c>
-      <c r="R3" s="432"/>
-      <c r="S3" s="432"/>
-      <c r="T3" s="432"/>
-      <c r="U3" s="433"/>
-      <c r="V3" s="431" t="str">
+      <c r="R3" s="459"/>
+      <c r="S3" s="459"/>
+      <c r="T3" s="459"/>
+      <c r="U3" s="460"/>
+      <c r="V3" s="458" t="str">
         <f>TEXT(AO1+3,"m月d日（aaa）")</f>
         <v>1月3日(火)</v>
       </c>
-      <c r="W3" s="432"/>
-      <c r="X3" s="432"/>
-      <c r="Y3" s="432"/>
-      <c r="Z3" s="432"/>
-      <c r="AA3" s="432"/>
-      <c r="AB3" s="431" t="str">
+      <c r="W3" s="459"/>
+      <c r="X3" s="459"/>
+      <c r="Y3" s="459"/>
+      <c r="Z3" s="459"/>
+      <c r="AA3" s="459"/>
+      <c r="AB3" s="458" t="str">
         <f>TEXT(AO1+4,"m月d日（aaa）")</f>
         <v>1月4日(水)</v>
       </c>
-      <c r="AC3" s="432"/>
-      <c r="AD3" s="432"/>
-      <c r="AE3" s="432"/>
-      <c r="AF3" s="432"/>
-      <c r="AG3" s="433"/>
-      <c r="AH3" s="444" t="str">
+      <c r="AC3" s="459"/>
+      <c r="AD3" s="459"/>
+      <c r="AE3" s="459"/>
+      <c r="AF3" s="459"/>
+      <c r="AG3" s="460"/>
+      <c r="AH3" s="442" t="str">
         <f>TEXT(AO1+5,"m月d日（aaa）")</f>
         <v>1月5日(木)</v>
       </c>
-      <c r="AI3" s="444"/>
-      <c r="AJ3" s="444"/>
-      <c r="AK3" s="445"/>
-      <c r="AN3" s="466" t="s">
+      <c r="AI3" s="442"/>
+      <c r="AJ3" s="442"/>
+      <c r="AK3" s="443"/>
+      <c r="AN3" s="421" t="s">
         <v>39</v>
       </c>
-      <c r="AO3" s="462" t="s">
+      <c r="AO3" s="417" t="s">
         <v>40</v>
       </c>
-      <c r="AP3" s="462" t="s">
+      <c r="AP3" s="417" t="s">
         <v>41</v>
       </c>
-      <c r="AQ3" s="462" t="s">
+      <c r="AQ3" s="417" t="s">
         <v>42</v>
       </c>
-      <c r="AR3" s="462" t="s">
+      <c r="AR3" s="417" t="s">
         <v>43</v>
       </c>
-      <c r="AS3" s="462" t="s">
+      <c r="AS3" s="417" t="s">
         <v>44</v>
       </c>
-      <c r="AT3" s="462" t="s">
+      <c r="AT3" s="417" t="s">
         <v>45</v>
       </c>
-      <c r="AU3" s="462" t="s">
+      <c r="AU3" s="417" t="s">
         <v>46</v>
       </c>
-      <c r="AV3" s="464" t="s">
+      <c r="AV3" s="419" t="s">
         <v>47</v>
       </c>
       <c r="BD3" s="4"/>
@@ -7085,10 +7085,10 @@
       <c r="CL3" s="4"/>
     </row>
     <row r="4" spans="1:90" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="424"/>
-      <c r="B4" s="425"/>
-      <c r="C4" s="428"/>
-      <c r="D4" s="429"/>
+      <c r="A4" s="451"/>
+      <c r="B4" s="452"/>
+      <c r="C4" s="455"/>
+      <c r="D4" s="456"/>
       <c r="E4" s="5">
         <v>1</v>
       </c>
@@ -7188,18 +7188,18 @@
       <c r="AK4" s="21">
         <v>4</v>
       </c>
-      <c r="AN4" s="467"/>
-      <c r="AO4" s="463"/>
-      <c r="AP4" s="463"/>
-      <c r="AQ4" s="463"/>
-      <c r="AR4" s="463"/>
-      <c r="AS4" s="463"/>
-      <c r="AT4" s="463"/>
-      <c r="AU4" s="463"/>
-      <c r="AV4" s="465"/>
+      <c r="AN4" s="422"/>
+      <c r="AO4" s="418"/>
+      <c r="AP4" s="418"/>
+      <c r="AQ4" s="418"/>
+      <c r="AR4" s="418"/>
+      <c r="AS4" s="418"/>
+      <c r="AT4" s="418"/>
+      <c r="AU4" s="418"/>
+      <c r="AV4" s="420"/>
     </row>
     <row r="5" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="441" t="s">
+      <c r="A5" s="439" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="22" t="s">
@@ -7263,11 +7263,11 @@
         <v>38</v>
       </c>
       <c r="AN5" s="389">
-        <f t="shared" ref="AN5:AU19" si="0">COUNTIF($E5:$AK5,AN$3)</f>
+        <f>COUNTIF($E5:$AK5,"*"&amp;AN$3&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="AO5" s="393">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AO5:AV19" si="0">COUNTIF($E5:$AK5,"*"&amp;AO$3&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="AP5" s="393">
@@ -7295,21 +7295,21 @@
         <v>0</v>
       </c>
       <c r="AV5" s="394">
-        <f t="shared" ref="AV5:AV19" si="1">COUNTIF($E5:$AK5,AV$3)+COUNTIF($E5:$AK5,"技術")+COUNTIF($E5:$AK5,"家庭")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="442"/>
+      <c r="A6" s="440"/>
       <c r="B6" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="254">
-        <f t="shared" ref="C6:D9" si="2">C22</f>
+        <f t="shared" ref="C6:D9" si="1">C22</f>
         <v>0</v>
       </c>
       <c r="D6" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E6" s="255"/>
@@ -7362,7 +7362,7 @@
         <v>38</v>
       </c>
       <c r="AN6" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AN6:AV19" si="2">COUNTIF($E6:$AK6,"*"&amp;AN$3&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="AO6" s="396">
@@ -7394,21 +7394,21 @@
         <v>0</v>
       </c>
       <c r="AV6" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="442"/>
+      <c r="A7" s="440"/>
       <c r="B7" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="254">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D7" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E7" s="255"/>
@@ -7461,7 +7461,7 @@
         <v>38</v>
       </c>
       <c r="AN7" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO7" s="396">
@@ -7493,21 +7493,21 @@
         <v>0</v>
       </c>
       <c r="AV7" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:90" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="442"/>
+      <c r="A8" s="440"/>
       <c r="B8" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="254">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D8" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E8" s="266"/>
@@ -7560,7 +7560,7 @@
         <v>38</v>
       </c>
       <c r="AN8" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO8" s="396">
@@ -7592,21 +7592,21 @@
         <v>0</v>
       </c>
       <c r="AV8" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="443"/>
+      <c r="A9" s="441"/>
       <c r="B9" s="35" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="278">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D9" s="279">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E9" s="280"/>
@@ -7659,7 +7659,7 @@
         <v>38</v>
       </c>
       <c r="AN9" s="398">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO9" s="399">
@@ -7691,12 +7691,12 @@
         <v>0</v>
       </c>
       <c r="AV9" s="400">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="441" t="s">
+      <c r="A10" s="439" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="AL10" s="47"/>
       <c r="AN10" s="401">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO10" s="402">
@@ -7793,12 +7793,12 @@
         <v>0</v>
       </c>
       <c r="AV10" s="403">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="442"/>
+      <c r="A11" s="440"/>
       <c r="B11" s="30" t="s">
         <v>5</v>
       </c>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AL11" s="47"/>
       <c r="AN11" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO11" s="396">
@@ -7893,12 +7893,12 @@
         <v>0</v>
       </c>
       <c r="AV11" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="442"/>
+      <c r="A12" s="440"/>
       <c r="B12" s="30" t="s">
         <v>6</v>
       </c>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AL12" s="47"/>
       <c r="AN12" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO12" s="396">
@@ -7993,12 +7993,12 @@
         <v>0</v>
       </c>
       <c r="AV12" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="442"/>
+      <c r="A13" s="440"/>
       <c r="B13" s="30" t="s">
         <v>7</v>
       </c>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AL13" s="47"/>
       <c r="AN13" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO13" s="396">
@@ -8093,12 +8093,12 @@
         <v>0</v>
       </c>
       <c r="AV13" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="443"/>
+      <c r="A14" s="441"/>
       <c r="B14" s="35" t="s">
         <v>8</v>
       </c>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AL14" s="47"/>
       <c r="AN14" s="404">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO14" s="405">
@@ -8193,12 +8193,12 @@
         <v>0</v>
       </c>
       <c r="AV14" s="406">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="442" t="s">
+      <c r="A15" s="440" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="22" t="s">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AL15" s="47"/>
       <c r="AN15" s="389">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO15" s="393">
@@ -8295,12 +8295,12 @@
         <v>0</v>
       </c>
       <c r="AV15" s="394">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="442"/>
+      <c r="A16" s="440"/>
       <c r="B16" s="30" t="s">
         <v>5</v>
       </c>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="AL16" s="47"/>
       <c r="AN16" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO16" s="396">
@@ -8395,12 +8395,12 @@
         <v>0</v>
       </c>
       <c r="AV16" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="442"/>
+      <c r="A17" s="440"/>
       <c r="B17" s="30" t="s">
         <v>6</v>
       </c>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AL17" s="47"/>
       <c r="AN17" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO17" s="396">
@@ -8495,12 +8495,12 @@
         <v>0</v>
       </c>
       <c r="AV17" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="442"/>
+      <c r="A18" s="440"/>
       <c r="B18" s="30" t="s">
         <v>7</v>
       </c>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AL18" s="47"/>
       <c r="AN18" s="395">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO18" s="396">
@@ -8595,12 +8595,12 @@
         <v>0</v>
       </c>
       <c r="AV18" s="397">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="442"/>
+      <c r="A19" s="440"/>
       <c r="B19" s="35" t="s">
         <v>8</v>
       </c>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="AL19" s="47"/>
       <c r="AN19" s="407">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AO19" s="408">
@@ -8695,12 +8695,12 @@
         <v>0</v>
       </c>
       <c r="AV19" s="409">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BD19" s="446"/>
-      <c r="BE19" s="447"/>
-      <c r="BF19" s="447"/>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD19" s="425"/>
+      <c r="BE19" s="426"/>
+      <c r="BF19" s="426"/>
       <c r="BJ19" s="56"/>
       <c r="BK19" s="56"/>
       <c r="BL19" s="56"/>
@@ -8787,7 +8787,7 @@
       <c r="BC20" s="392"/>
     </row>
     <row r="21" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="442" t="s">
+      <c r="A21" s="440" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="68" t="s">
@@ -8903,7 +8903,7 @@
       <c r="BI21" s="81"/>
     </row>
     <row r="22" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="442"/>
+      <c r="A22" s="440"/>
       <c r="B22" s="82" t="s">
         <v>28</v>
       </c>
@@ -9017,7 +9017,7 @@
       <c r="BI22" s="81"/>
     </row>
     <row r="23" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="442"/>
+      <c r="A23" s="440"/>
       <c r="B23" s="90" t="s">
         <v>29</v>
       </c>
@@ -9131,7 +9131,7 @@
       <c r="BI23" s="81"/>
     </row>
     <row r="24" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="442"/>
+      <c r="A24" s="440"/>
       <c r="B24" s="98" t="s">
         <v>7</v>
       </c>
@@ -9245,7 +9245,7 @@
       <c r="BI24" s="81"/>
     </row>
     <row r="25" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="442"/>
+      <c r="A25" s="440"/>
       <c r="B25" s="98" t="s">
         <v>8</v>
       </c>
@@ -9359,7 +9359,7 @@
       <c r="BI25" s="81"/>
     </row>
     <row r="26" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="442"/>
+      <c r="A26" s="440"/>
       <c r="B26" s="99" t="s">
         <v>30</v>
       </c>
@@ -9473,7 +9473,7 @@
       <c r="BI26" s="81"/>
     </row>
     <row r="27" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="442"/>
+      <c r="A27" s="440"/>
       <c r="B27" s="82" t="s">
         <v>30</v>
       </c>
@@ -9587,7 +9587,7 @@
       <c r="BI27" s="81"/>
     </row>
     <row r="28" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="442"/>
+      <c r="A28" s="440"/>
       <c r="B28" s="82" t="s">
         <v>30</v>
       </c>
@@ -9701,7 +9701,7 @@
       <c r="BI28" s="81"/>
     </row>
     <row r="29" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="442"/>
+      <c r="A29" s="440"/>
       <c r="B29" s="82" t="s">
         <v>30</v>
       </c>
@@ -9815,7 +9815,7 @@
       <c r="BI29" s="81"/>
     </row>
     <row r="30" spans="1:90" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="442"/>
+      <c r="A30" s="440"/>
       <c r="B30" s="82" t="s">
         <v>30</v>
       </c>
@@ -9929,7 +9929,7 @@
       <c r="BI30" s="81"/>
     </row>
     <row r="31" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="441" t="s">
+      <c r="A31" s="439" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="115" t="s">
@@ -10045,7 +10045,7 @@
       <c r="BI31" s="81"/>
     </row>
     <row r="32" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="442"/>
+      <c r="A32" s="440"/>
       <c r="B32" s="132" t="s">
         <v>28</v>
       </c>
@@ -10159,7 +10159,7 @@
       <c r="BI32" s="81"/>
     </row>
     <row r="33" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="442"/>
+      <c r="A33" s="440"/>
       <c r="B33" s="68" t="s">
         <v>29</v>
       </c>
@@ -10273,7 +10273,7 @@
       <c r="BI33" s="81"/>
     </row>
     <row r="34" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="442"/>
+      <c r="A34" s="440"/>
       <c r="B34" s="132" t="s">
         <v>32</v>
       </c>
@@ -10387,7 +10387,7 @@
       <c r="BI34" s="81"/>
     </row>
     <row r="35" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="442"/>
+      <c r="A35" s="440"/>
       <c r="B35" s="143" t="s">
         <v>33</v>
       </c>
@@ -10501,7 +10501,7 @@
       <c r="BI35" s="81"/>
     </row>
     <row r="36" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="442"/>
+      <c r="A36" s="440"/>
       <c r="B36" s="149" t="s">
         <v>30</v>
       </c>
@@ -10615,7 +10615,7 @@
       <c r="BI36" s="81"/>
     </row>
     <row r="37" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="442"/>
+      <c r="A37" s="440"/>
       <c r="B37" s="82" t="s">
         <v>30</v>
       </c>
@@ -10729,7 +10729,7 @@
       <c r="BI37" s="81"/>
     </row>
     <row r="38" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="442"/>
+      <c r="A38" s="440"/>
       <c r="B38" s="154" t="s">
         <v>30</v>
       </c>
@@ -10843,7 +10843,7 @@
       <c r="BI38" s="81"/>
     </row>
     <row r="39" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="442"/>
+      <c r="A39" s="440"/>
       <c r="B39" s="154" t="s">
         <v>30</v>
       </c>
@@ -10957,7 +10957,7 @@
       <c r="BI39" s="81"/>
     </row>
     <row r="40" spans="1:61" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="443"/>
+      <c r="A40" s="441"/>
       <c r="B40" s="165" t="s">
         <v>30</v>
       </c>
@@ -11071,7 +11071,7 @@
       <c r="BI40" s="81"/>
     </row>
     <row r="41" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="441" t="s">
+      <c r="A41" s="439" t="s">
         <v>34</v>
       </c>
       <c r="B41" s="169" t="s">
@@ -11187,7 +11187,7 @@
       <c r="BI41" s="81"/>
     </row>
     <row r="42" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="442"/>
+      <c r="A42" s="440"/>
       <c r="B42" s="170" t="s">
         <v>28</v>
       </c>
@@ -11301,7 +11301,7 @@
       <c r="BI42" s="81"/>
     </row>
     <row r="43" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="442"/>
+      <c r="A43" s="440"/>
       <c r="B43" s="181" t="s">
         <v>29</v>
       </c>
@@ -11415,7 +11415,7 @@
       <c r="BI43" s="81"/>
     </row>
     <row r="44" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="442"/>
+      <c r="A44" s="440"/>
       <c r="B44" s="182" t="s">
         <v>32</v>
       </c>
@@ -11529,7 +11529,7 @@
       <c r="BI44" s="81"/>
     </row>
     <row r="45" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="442"/>
+      <c r="A45" s="440"/>
       <c r="B45" s="187" t="s">
         <v>33</v>
       </c>
@@ -11643,7 +11643,7 @@
       <c r="BI45" s="81"/>
     </row>
     <row r="46" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="442"/>
+      <c r="A46" s="440"/>
       <c r="B46" s="194" t="s">
         <v>30</v>
       </c>
@@ -11757,7 +11757,7 @@
       <c r="BI46" s="81"/>
     </row>
     <row r="47" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="442"/>
+      <c r="A47" s="440"/>
       <c r="B47" s="195" t="s">
         <v>30</v>
       </c>
@@ -11871,7 +11871,7 @@
       <c r="BI47" s="81"/>
     </row>
     <row r="48" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="442"/>
+      <c r="A48" s="440"/>
       <c r="B48" s="195" t="s">
         <v>30</v>
       </c>
@@ -11985,7 +11985,7 @@
       <c r="BI48" s="81"/>
     </row>
     <row r="49" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="442"/>
+      <c r="A49" s="440"/>
       <c r="B49" s="195" t="s">
         <v>30</v>
       </c>
@@ -12099,7 +12099,7 @@
       <c r="BI49" s="81"/>
     </row>
     <row r="50" spans="1:61" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="443"/>
+      <c r="A50" s="441"/>
       <c r="B50" s="205" t="s">
         <v>30</v>
       </c>
@@ -12213,7 +12213,7 @@
       <c r="BI50" s="81"/>
     </row>
     <row r="51" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="441" t="s">
+      <c r="A51" s="439" t="s">
         <v>35</v>
       </c>
       <c r="B51" s="220" t="s">
@@ -12329,7 +12329,7 @@
       <c r="BI51" s="81"/>
     </row>
     <row r="52" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="442"/>
+      <c r="A52" s="440"/>
       <c r="B52" s="230" t="s">
         <v>36</v>
       </c>
@@ -12443,7 +12443,7 @@
       <c r="BI52" s="81"/>
     </row>
     <row r="53" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="442"/>
+      <c r="A53" s="440"/>
       <c r="B53" s="230" t="s">
         <v>36</v>
       </c>
@@ -12557,7 +12557,7 @@
       <c r="BI53" s="81"/>
     </row>
     <row r="54" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="442"/>
+      <c r="A54" s="440"/>
       <c r="B54" s="230" t="s">
         <v>36</v>
       </c>
@@ -12671,7 +12671,7 @@
       <c r="BI54" s="81"/>
     </row>
     <row r="55" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="442"/>
+      <c r="A55" s="440"/>
       <c r="B55" s="230" t="s">
         <v>36</v>
       </c>
@@ -12785,7 +12785,7 @@
       <c r="BI55" s="81"/>
     </row>
     <row r="56" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="442"/>
+      <c r="A56" s="440"/>
       <c r="B56" s="230" t="s">
         <v>36</v>
       </c>
@@ -12899,7 +12899,7 @@
       <c r="BI56" s="81"/>
     </row>
     <row r="57" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="442"/>
+      <c r="A57" s="440"/>
       <c r="B57" s="230" t="s">
         <v>36</v>
       </c>
@@ -13013,7 +13013,7 @@
       <c r="BI57" s="81"/>
     </row>
     <row r="58" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="442"/>
+      <c r="A58" s="440"/>
       <c r="B58" s="230" t="s">
         <v>36</v>
       </c>
@@ -13127,7 +13127,7 @@
       <c r="BI58" s="81"/>
     </row>
     <row r="59" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="442"/>
+      <c r="A59" s="440"/>
       <c r="B59" s="230" t="s">
         <v>36</v>
       </c>
@@ -13241,7 +13241,7 @@
       <c r="BI59" s="81"/>
     </row>
     <row r="60" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="442"/>
+      <c r="A60" s="440"/>
       <c r="B60" s="230" t="s">
         <v>36</v>
       </c>
@@ -13355,7 +13355,7 @@
       <c r="BI60" s="81"/>
     </row>
     <row r="61" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="442"/>
+      <c r="A61" s="440"/>
       <c r="B61" s="230" t="s">
         <v>36</v>
       </c>
@@ -13469,7 +13469,7 @@
       <c r="BI61" s="81"/>
     </row>
     <row r="62" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="442"/>
+      <c r="A62" s="440"/>
       <c r="B62" s="230" t="s">
         <v>36</v>
       </c>
@@ -13583,7 +13583,7 @@
       <c r="BI62" s="81"/>
     </row>
     <row r="63" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="442"/>
+      <c r="A63" s="440"/>
       <c r="B63" s="230" t="s">
         <v>36</v>
       </c>
@@ -13697,7 +13697,7 @@
       <c r="BI63" s="81"/>
     </row>
     <row r="64" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="442"/>
+      <c r="A64" s="440"/>
       <c r="B64" s="230" t="s">
         <v>36</v>
       </c>
@@ -13811,7 +13811,7 @@
       <c r="BI64" s="81"/>
     </row>
     <row r="65" spans="1:90" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="443"/>
+      <c r="A65" s="441"/>
       <c r="B65" s="238" t="s">
         <v>36</v>
       </c>
@@ -13925,45 +13925,45 @@
       <c r="BI65" s="81"/>
     </row>
     <row r="66" spans="1:90" s="246" customFormat="1" ht="52.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="450"/>
-      <c r="B66" s="451"/>
-      <c r="C66" s="451"/>
-      <c r="D66" s="452"/>
-      <c r="E66" s="453"/>
-      <c r="F66" s="454"/>
-      <c r="G66" s="454"/>
-      <c r="H66" s="454"/>
-      <c r="I66" s="454"/>
-      <c r="J66" s="455"/>
-      <c r="K66" s="456"/>
-      <c r="L66" s="457"/>
-      <c r="M66" s="457"/>
-      <c r="N66" s="457"/>
-      <c r="O66" s="457"/>
-      <c r="P66" s="458"/>
-      <c r="Q66" s="456"/>
-      <c r="R66" s="457"/>
-      <c r="S66" s="457"/>
-      <c r="T66" s="457"/>
-      <c r="U66" s="458"/>
-      <c r="V66" s="456"/>
-      <c r="W66" s="457"/>
-      <c r="X66" s="457"/>
-      <c r="Y66" s="457"/>
-      <c r="Z66" s="457"/>
-      <c r="AA66" s="458"/>
-      <c r="AB66" s="456"/>
-      <c r="AC66" s="457"/>
-      <c r="AD66" s="457"/>
-      <c r="AE66" s="457"/>
-      <c r="AF66" s="457"/>
-      <c r="AG66" s="458"/>
-      <c r="AH66" s="459" t="e">
+      <c r="A66" s="427"/>
+      <c r="B66" s="428"/>
+      <c r="C66" s="428"/>
+      <c r="D66" s="429"/>
+      <c r="E66" s="430"/>
+      <c r="F66" s="431"/>
+      <c r="G66" s="431"/>
+      <c r="H66" s="431"/>
+      <c r="I66" s="431"/>
+      <c r="J66" s="432"/>
+      <c r="K66" s="433"/>
+      <c r="L66" s="434"/>
+      <c r="M66" s="434"/>
+      <c r="N66" s="434"/>
+      <c r="O66" s="434"/>
+      <c r="P66" s="435"/>
+      <c r="Q66" s="433"/>
+      <c r="R66" s="434"/>
+      <c r="S66" s="434"/>
+      <c r="T66" s="434"/>
+      <c r="U66" s="435"/>
+      <c r="V66" s="433"/>
+      <c r="W66" s="434"/>
+      <c r="X66" s="434"/>
+      <c r="Y66" s="434"/>
+      <c r="Z66" s="434"/>
+      <c r="AA66" s="435"/>
+      <c r="AB66" s="433"/>
+      <c r="AC66" s="434"/>
+      <c r="AD66" s="434"/>
+      <c r="AE66" s="434"/>
+      <c r="AF66" s="434"/>
+      <c r="AG66" s="435"/>
+      <c r="AH66" s="436" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI66" s="460"/>
-      <c r="AJ66" s="460"/>
-      <c r="AK66" s="461"/>
+      <c r="AI66" s="437"/>
+      <c r="AJ66" s="437"/>
+      <c r="AK66" s="438"/>
       <c r="AN66" s="410" t="s">
         <v>11</v>
       </c>
@@ -14051,10 +14051,10 @@
       </c>
     </row>
     <row r="77" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C77" s="448" t="s">
+      <c r="C77" s="423" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="449"/>
+      <c r="D77" s="424"/>
       <c r="E77" s="1">
         <f>COUNTIF(E$21:E$65,"*"&amp;$C77&amp;"*")</f>
         <v>0</v>
@@ -14189,10 +14189,10 @@
       </c>
     </row>
     <row r="78" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C78" s="448" t="s">
+      <c r="C78" s="423" t="s">
         <v>49</v>
       </c>
-      <c r="D78" s="449"/>
+      <c r="D78" s="424"/>
       <c r="E78" s="1">
         <f t="shared" ref="E78:T96" si="14">COUNTIF(E$21:E$65,"*"&amp;$C78&amp;"*")</f>
         <v>0</v>
@@ -14327,10 +14327,10 @@
       </c>
     </row>
     <row r="79" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C79" s="448" t="s">
+      <c r="C79" s="423" t="s">
         <v>50</v>
       </c>
-      <c r="D79" s="449"/>
+      <c r="D79" s="424"/>
       <c r="E79" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14465,10 +14465,10 @@
       </c>
     </row>
     <row r="80" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C80" s="448" t="s">
+      <c r="C80" s="423" t="s">
         <v>51</v>
       </c>
-      <c r="D80" s="449"/>
+      <c r="D80" s="424"/>
       <c r="E80" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14603,10 +14603,10 @@
       </c>
     </row>
     <row r="81" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C81" s="448" t="s">
+      <c r="C81" s="423" t="s">
         <v>17</v>
       </c>
-      <c r="D81" s="449"/>
+      <c r="D81" s="424"/>
       <c r="E81" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14741,10 +14741,10 @@
       </c>
     </row>
     <row r="82" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C82" s="448" t="s">
+      <c r="C82" s="423" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="449"/>
+      <c r="D82" s="424"/>
       <c r="E82" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14879,10 +14879,10 @@
       </c>
     </row>
     <row r="83" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C83" s="448" t="s">
+      <c r="C83" s="423" t="s">
         <v>52</v>
       </c>
-      <c r="D83" s="449"/>
+      <c r="D83" s="424"/>
       <c r="E83" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15017,10 +15017,10 @@
       </c>
     </row>
     <row r="84" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C84" s="448" t="s">
+      <c r="C84" s="423" t="s">
         <v>22</v>
       </c>
-      <c r="D84" s="449"/>
+      <c r="D84" s="424"/>
       <c r="E84" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15155,10 +15155,10 @@
       </c>
     </row>
     <row r="85" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C85" s="448" t="s">
+      <c r="C85" s="423" t="s">
         <v>23</v>
       </c>
-      <c r="D85" s="449"/>
+      <c r="D85" s="424"/>
       <c r="E85" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15293,10 +15293,10 @@
       </c>
     </row>
     <row r="86" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C86" s="448" t="s">
+      <c r="C86" s="423" t="s">
         <v>53</v>
       </c>
-      <c r="D86" s="449"/>
+      <c r="D86" s="424"/>
       <c r="E86" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15431,10 +15431,10 @@
       </c>
     </row>
     <row r="87" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C87" s="448" t="s">
+      <c r="C87" s="423" t="s">
         <v>54</v>
       </c>
-      <c r="D87" s="449"/>
+      <c r="D87" s="424"/>
       <c r="E87" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15569,10 +15569,10 @@
       </c>
     </row>
     <row r="88" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C88" s="448" t="s">
+      <c r="C88" s="423" t="s">
         <v>55</v>
       </c>
-      <c r="D88" s="449"/>
+      <c r="D88" s="424"/>
       <c r="E88" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15707,10 +15707,10 @@
       </c>
     </row>
     <row r="89" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C89" s="448" t="s">
+      <c r="C89" s="423" t="s">
         <v>56</v>
       </c>
-      <c r="D89" s="449"/>
+      <c r="D89" s="424"/>
       <c r="E89" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15845,10 +15845,10 @@
       </c>
     </row>
     <row r="90" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C90" s="448" t="s">
+      <c r="C90" s="423" t="s">
         <v>57</v>
       </c>
-      <c r="D90" s="449"/>
+      <c r="D90" s="424"/>
       <c r="E90" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -15983,10 +15983,10 @@
       </c>
     </row>
     <row r="91" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C91" s="448" t="s">
+      <c r="C91" s="423" t="s">
         <v>58</v>
       </c>
-      <c r="D91" s="449"/>
+      <c r="D91" s="424"/>
       <c r="E91" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16121,10 +16121,10 @@
       </c>
     </row>
     <row r="92" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C92" s="448">
-        <v>0</v>
-      </c>
-      <c r="D92" s="449"/>
+      <c r="C92" s="423">
+        <v>0</v>
+      </c>
+      <c r="D92" s="424"/>
       <c r="E92" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16259,10 +16259,10 @@
       </c>
     </row>
     <row r="93" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C93" s="448">
-        <v>0</v>
-      </c>
-      <c r="D93" s="449"/>
+      <c r="C93" s="423">
+        <v>0</v>
+      </c>
+      <c r="D93" s="424"/>
       <c r="E93" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16397,10 +16397,10 @@
       </c>
     </row>
     <row r="94" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C94" s="448">
-        <v>0</v>
-      </c>
-      <c r="D94" s="449"/>
+      <c r="C94" s="423">
+        <v>0</v>
+      </c>
+      <c r="D94" s="424"/>
       <c r="E94" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16535,10 +16535,10 @@
       </c>
     </row>
     <row r="95" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C95" s="448">
-        <v>0</v>
-      </c>
-      <c r="D95" s="449"/>
+      <c r="C95" s="423">
+        <v>0</v>
+      </c>
+      <c r="D95" s="424"/>
       <c r="E95" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -16673,10 +16673,10 @@
       </c>
     </row>
     <row r="96" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C96" s="448">
-        <v>0</v>
-      </c>
-      <c r="D96" s="449"/>
+      <c r="C96" s="423">
+        <v>0</v>
+      </c>
+      <c r="D96" s="424"/>
       <c r="E96" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -25108,30 +25108,26 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="60">
-    <mergeCell ref="AU3:AU4"/>
-    <mergeCell ref="AV3:AV4"/>
-    <mergeCell ref="AR3:AR4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AS3:AS4"/>
-    <mergeCell ref="AT3:AT4"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="AB1:AE2"/>
+    <mergeCell ref="AF1:AG2"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:X2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="A41:A50"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="AH3:AK3"/>
     <mergeCell ref="BD19:BF19"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A66:D66"/>
@@ -25148,26 +25144,30 @@
     <mergeCell ref="A51:A65"/>
     <mergeCell ref="A21:A30"/>
     <mergeCell ref="A31:A40"/>
-    <mergeCell ref="A41:A50"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="AH3:AK3"/>
-    <mergeCell ref="AB1:AE2"/>
-    <mergeCell ref="AF1:AG2"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="V3:AA3"/>
-    <mergeCell ref="AB3:AG3"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="AU3:AU4"/>
+    <mergeCell ref="AV3:AV4"/>
+    <mergeCell ref="AR3:AR4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AP3:AP4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="AS3:AS4"/>
+    <mergeCell ref="AT3:AT4"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C5:D19">

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksuga\.gemini\antigravity\scratch\create-timetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856F6C18-294E-480E-A318-05A14C156786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BA769D-2D5E-47EB-91A1-9C059277C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F317536C-8130-47EB-BB07-191DD2A1D9B2}"/>
   </bookViews>
@@ -5359,34 +5359,105 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="232" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="242" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="261" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="262" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="241" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="260" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5434,94 +5505,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="242" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="261" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="243" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="262" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="241" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="260" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6873,53 +6873,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:90" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="461"/>
-      <c r="B1" s="461"/>
-      <c r="C1" s="461"/>
-      <c r="D1" s="461"/>
-      <c r="E1" s="462" t="str">
+      <c r="A1" s="434"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="435" t="str">
         <f>_xlfn.CONCAT("【週案",AN1,"】　",TEXT(AO1,"[$-ja-JP]ge.m.d")," ～ ",TEXT(AP1,"[$-ja-JP]ge.m.d"))</f>
         <v>【週案】　M33.1.0 ～ M33.1.0</v>
       </c>
-      <c r="F1" s="462"/>
-      <c r="G1" s="462"/>
-      <c r="H1" s="462"/>
-      <c r="I1" s="462"/>
-      <c r="J1" s="462"/>
-      <c r="K1" s="462"/>
-      <c r="L1" s="462"/>
-      <c r="M1" s="462"/>
-      <c r="N1" s="462"/>
-      <c r="O1" s="462"/>
-      <c r="P1" s="462"/>
-      <c r="Q1" s="462"/>
-      <c r="R1" s="462"/>
-      <c r="S1" s="462"/>
-      <c r="T1" s="462"/>
-      <c r="U1" s="462"/>
-      <c r="V1" s="462"/>
-      <c r="W1" s="462"/>
-      <c r="X1" s="462"/>
-      <c r="Y1" s="464" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z1" s="444">
+      <c r="F1" s="435"/>
+      <c r="G1" s="435"/>
+      <c r="H1" s="435"/>
+      <c r="I1" s="435"/>
+      <c r="J1" s="435"/>
+      <c r="K1" s="435"/>
+      <c r="L1" s="435"/>
+      <c r="M1" s="435"/>
+      <c r="N1" s="435"/>
+      <c r="O1" s="435"/>
+      <c r="P1" s="435"/>
+      <c r="Q1" s="435"/>
+      <c r="R1" s="435"/>
+      <c r="S1" s="435"/>
+      <c r="T1" s="435"/>
+      <c r="U1" s="435"/>
+      <c r="V1" s="435"/>
+      <c r="W1" s="435"/>
+      <c r="X1" s="435"/>
+      <c r="Y1" s="437" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="417">
         <v>1</v>
       </c>
-      <c r="AA1" s="466" t="s">
+      <c r="AA1" s="439" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="444" t="s">
+      <c r="AB1" s="417" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="444"/>
-      <c r="AD1" s="444"/>
-      <c r="AE1" s="444"/>
-      <c r="AF1" s="446">
+      <c r="AC1" s="417"/>
+      <c r="AD1" s="417"/>
+      <c r="AE1" s="417"/>
+      <c r="AF1" s="419">
         <f ca="1">NOW()</f>
-        <v>46191.035811458336</v>
-      </c>
-      <c r="AG1" s="446"/>
+        <v>46191.038034722224</v>
+      </c>
+      <c r="AG1" s="419"/>
       <c r="AH1" s="376"/>
       <c r="AI1" s="376"/>
       <c r="AJ1" s="376"/>
@@ -6927,39 +6927,39 @@
       <c r="AL1" s="376"/>
     </row>
     <row r="2" spans="1:90" ht="25.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="448"/>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="463"/>
-      <c r="F2" s="463"/>
-      <c r="G2" s="463"/>
-      <c r="H2" s="463"/>
-      <c r="I2" s="463"/>
-      <c r="J2" s="463"/>
-      <c r="K2" s="463"/>
-      <c r="L2" s="463"/>
-      <c r="M2" s="463"/>
-      <c r="N2" s="463"/>
-      <c r="O2" s="463"/>
-      <c r="P2" s="463"/>
-      <c r="Q2" s="463"/>
-      <c r="R2" s="463"/>
-      <c r="S2" s="463"/>
-      <c r="T2" s="463"/>
-      <c r="U2" s="463"/>
-      <c r="V2" s="463"/>
-      <c r="W2" s="463"/>
-      <c r="X2" s="463"/>
-      <c r="Y2" s="465"/>
-      <c r="Z2" s="445"/>
-      <c r="AA2" s="467"/>
-      <c r="AB2" s="445"/>
-      <c r="AC2" s="445"/>
-      <c r="AD2" s="445"/>
-      <c r="AE2" s="445"/>
-      <c r="AF2" s="447"/>
-      <c r="AG2" s="447"/>
+      <c r="A2" s="421"/>
+      <c r="B2" s="421"/>
+      <c r="C2" s="421"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="436"/>
+      <c r="F2" s="436"/>
+      <c r="G2" s="436"/>
+      <c r="H2" s="436"/>
+      <c r="I2" s="436"/>
+      <c r="J2" s="436"/>
+      <c r="K2" s="436"/>
+      <c r="L2" s="436"/>
+      <c r="M2" s="436"/>
+      <c r="N2" s="436"/>
+      <c r="O2" s="436"/>
+      <c r="P2" s="436"/>
+      <c r="Q2" s="436"/>
+      <c r="R2" s="436"/>
+      <c r="S2" s="436"/>
+      <c r="T2" s="436"/>
+      <c r="U2" s="436"/>
+      <c r="V2" s="436"/>
+      <c r="W2" s="436"/>
+      <c r="X2" s="436"/>
+      <c r="Y2" s="438"/>
+      <c r="Z2" s="418"/>
+      <c r="AA2" s="440"/>
+      <c r="AB2" s="418"/>
+      <c r="AC2" s="418"/>
+      <c r="AD2" s="418"/>
+      <c r="AE2" s="418"/>
+      <c r="AF2" s="420"/>
+      <c r="AG2" s="420"/>
       <c r="AH2" s="376"/>
       <c r="AI2" s="376"/>
       <c r="AJ2" s="376"/>
@@ -6967,86 +6967,86 @@
       <c r="AL2" s="376"/>
     </row>
     <row r="3" spans="1:90" s="2" customFormat="1" ht="18.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="449"/>
-      <c r="B3" s="450"/>
-      <c r="C3" s="453"/>
-      <c r="D3" s="454"/>
-      <c r="E3" s="457" t="str">
+      <c r="A3" s="422"/>
+      <c r="B3" s="423"/>
+      <c r="C3" s="426"/>
+      <c r="D3" s="427"/>
+      <c r="E3" s="430" t="str">
         <f>TEXT(AO1,"m月d日（aaa）")</f>
         <v>1月0日(土)</v>
       </c>
-      <c r="F3" s="457"/>
-      <c r="G3" s="457"/>
-      <c r="H3" s="457"/>
-      <c r="I3" s="457"/>
-      <c r="J3" s="457"/>
-      <c r="K3" s="458" t="str">
+      <c r="F3" s="430"/>
+      <c r="G3" s="430"/>
+      <c r="H3" s="430"/>
+      <c r="I3" s="430"/>
+      <c r="J3" s="430"/>
+      <c r="K3" s="431" t="str">
         <f>TEXT(AO1+1,"m月d日（aaa）")</f>
         <v>1月1日(日)</v>
       </c>
-      <c r="L3" s="459"/>
-      <c r="M3" s="459"/>
-      <c r="N3" s="459"/>
-      <c r="O3" s="459"/>
-      <c r="P3" s="460"/>
-      <c r="Q3" s="458" t="str">
+      <c r="L3" s="432"/>
+      <c r="M3" s="432"/>
+      <c r="N3" s="432"/>
+      <c r="O3" s="432"/>
+      <c r="P3" s="433"/>
+      <c r="Q3" s="431" t="str">
         <f>TEXT(AO1+2,"m月d日（aaa）")</f>
         <v>1月2日(月)</v>
       </c>
-      <c r="R3" s="459"/>
-      <c r="S3" s="459"/>
-      <c r="T3" s="459"/>
-      <c r="U3" s="460"/>
-      <c r="V3" s="458" t="str">
+      <c r="R3" s="432"/>
+      <c r="S3" s="432"/>
+      <c r="T3" s="432"/>
+      <c r="U3" s="433"/>
+      <c r="V3" s="431" t="str">
         <f>TEXT(AO1+3,"m月d日（aaa）")</f>
         <v>1月3日(火)</v>
       </c>
-      <c r="W3" s="459"/>
-      <c r="X3" s="459"/>
-      <c r="Y3" s="459"/>
-      <c r="Z3" s="459"/>
-      <c r="AA3" s="459"/>
-      <c r="AB3" s="458" t="str">
+      <c r="W3" s="432"/>
+      <c r="X3" s="432"/>
+      <c r="Y3" s="432"/>
+      <c r="Z3" s="432"/>
+      <c r="AA3" s="432"/>
+      <c r="AB3" s="431" t="str">
         <f>TEXT(AO1+4,"m月d日（aaa）")</f>
         <v>1月4日(水)</v>
       </c>
-      <c r="AC3" s="459"/>
-      <c r="AD3" s="459"/>
-      <c r="AE3" s="459"/>
-      <c r="AF3" s="459"/>
-      <c r="AG3" s="460"/>
-      <c r="AH3" s="442" t="str">
+      <c r="AC3" s="432"/>
+      <c r="AD3" s="432"/>
+      <c r="AE3" s="432"/>
+      <c r="AF3" s="432"/>
+      <c r="AG3" s="433"/>
+      <c r="AH3" s="444" t="str">
         <f>TEXT(AO1+5,"m月d日（aaa）")</f>
         <v>1月5日(木)</v>
       </c>
-      <c r="AI3" s="442"/>
-      <c r="AJ3" s="442"/>
-      <c r="AK3" s="443"/>
-      <c r="AN3" s="421" t="s">
+      <c r="AI3" s="444"/>
+      <c r="AJ3" s="444"/>
+      <c r="AK3" s="445"/>
+      <c r="AN3" s="466" t="s">
         <v>39</v>
       </c>
-      <c r="AO3" s="417" t="s">
+      <c r="AO3" s="462" t="s">
         <v>40</v>
       </c>
-      <c r="AP3" s="417" t="s">
+      <c r="AP3" s="462" t="s">
         <v>41</v>
       </c>
-      <c r="AQ3" s="417" t="s">
+      <c r="AQ3" s="462" t="s">
         <v>42</v>
       </c>
-      <c r="AR3" s="417" t="s">
+      <c r="AR3" s="462" t="s">
         <v>43</v>
       </c>
-      <c r="AS3" s="417" t="s">
+      <c r="AS3" s="462" t="s">
         <v>44</v>
       </c>
-      <c r="AT3" s="417" t="s">
+      <c r="AT3" s="462" t="s">
         <v>45</v>
       </c>
-      <c r="AU3" s="417" t="s">
+      <c r="AU3" s="462" t="s">
         <v>46</v>
       </c>
-      <c r="AV3" s="419" t="s">
+      <c r="AV3" s="464" t="s">
         <v>47</v>
       </c>
       <c r="BD3" s="4"/>
@@ -7085,10 +7085,10 @@
       <c r="CL3" s="4"/>
     </row>
     <row r="4" spans="1:90" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="451"/>
-      <c r="B4" s="452"/>
-      <c r="C4" s="455"/>
-      <c r="D4" s="456"/>
+      <c r="A4" s="424"/>
+      <c r="B4" s="425"/>
+      <c r="C4" s="428"/>
+      <c r="D4" s="429"/>
       <c r="E4" s="5">
         <v>1</v>
       </c>
@@ -7188,18 +7188,18 @@
       <c r="AK4" s="21">
         <v>4</v>
       </c>
-      <c r="AN4" s="422"/>
-      <c r="AO4" s="418"/>
-      <c r="AP4" s="418"/>
-      <c r="AQ4" s="418"/>
-      <c r="AR4" s="418"/>
-      <c r="AS4" s="418"/>
-      <c r="AT4" s="418"/>
-      <c r="AU4" s="418"/>
-      <c r="AV4" s="420"/>
+      <c r="AN4" s="467"/>
+      <c r="AO4" s="463"/>
+      <c r="AP4" s="463"/>
+      <c r="AQ4" s="463"/>
+      <c r="AR4" s="463"/>
+      <c r="AS4" s="463"/>
+      <c r="AT4" s="463"/>
+      <c r="AU4" s="463"/>
+      <c r="AV4" s="465"/>
     </row>
     <row r="5" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="439" t="s">
+      <c r="A5" s="441" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="22" t="s">
@@ -7295,12 +7295,12 @@
         <v>0</v>
       </c>
       <c r="AV5" s="394">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($E5:$AK5,"*"&amp;AV$3&amp;"*")+COUNTIF($E5:$AK5,"*"&amp;"技術"&amp;"*")+COUNTIF($E5:$AK5,"*"&amp;"家庭"&amp;"*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="440"/>
+      <c r="A6" s="442"/>
       <c r="B6" s="30" t="s">
         <v>5</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>38</v>
       </c>
       <c r="AN6" s="395">
-        <f t="shared" ref="AN6:AV19" si="2">COUNTIF($E6:$AK6,"*"&amp;AN$3&amp;"*")</f>
+        <f t="shared" ref="AN6:AN19" si="2">COUNTIF($E6:$AK6,"*"&amp;AN$3&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="AO6" s="396">
@@ -7394,12 +7394,12 @@
         <v>0</v>
       </c>
       <c r="AV6" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AV6:AV19" si="3">COUNTIF($E6:$AK6,"*"&amp;AV$3&amp;"*")+COUNTIF($E6:$AK6,"*"&amp;"技術"&amp;"*")+COUNTIF($E6:$AK6,"*"&amp;"家庭"&amp;"*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="440"/>
+      <c r="A7" s="442"/>
       <c r="B7" s="30" t="s">
         <v>6</v>
       </c>
@@ -7493,12 +7493,12 @@
         <v>0</v>
       </c>
       <c r="AV7" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:90" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="440"/>
+      <c r="A8" s="442"/>
       <c r="B8" s="30" t="s">
         <v>7</v>
       </c>
@@ -7592,12 +7592,12 @@
         <v>0</v>
       </c>
       <c r="AV8" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="441"/>
+      <c r="A9" s="443"/>
       <c r="B9" s="35" t="s">
         <v>8</v>
       </c>
@@ -7691,12 +7691,12 @@
         <v>0</v>
       </c>
       <c r="AV9" s="400">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="439" t="s">
+      <c r="A10" s="441" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -7793,21 +7793,21 @@
         <v>0</v>
       </c>
       <c r="AV10" s="403">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="440"/>
+      <c r="A11" s="442"/>
       <c r="B11" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="296">
-        <f t="shared" ref="C11:D14" si="3">C32</f>
+        <f t="shared" ref="C11:D14" si="4">C32</f>
         <v>0</v>
       </c>
       <c r="D11" s="188">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E11" s="266"/>
@@ -7893,21 +7893,21 @@
         <v>0</v>
       </c>
       <c r="AV11" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="440"/>
+      <c r="A12" s="442"/>
       <c r="B12" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="300">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D12" s="188">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E12" s="266"/>
@@ -7993,21 +7993,21 @@
         <v>0</v>
       </c>
       <c r="AV12" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="440"/>
+      <c r="A13" s="442"/>
       <c r="B13" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D13" s="188">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E13" s="266"/>
@@ -8093,21 +8093,21 @@
         <v>0</v>
       </c>
       <c r="AV13" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="441"/>
+      <c r="A14" s="443"/>
       <c r="B14" s="35" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="301">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D14" s="279">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E14" s="302"/>
@@ -8193,12 +8193,12 @@
         <v>0</v>
       </c>
       <c r="AV14" s="406">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="440" t="s">
+      <c r="A15" s="442" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="22" t="s">
@@ -8295,21 +8295,21 @@
         <v>0</v>
       </c>
       <c r="AV15" s="394">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="440"/>
+      <c r="A16" s="442"/>
       <c r="B16" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="307">
-        <f t="shared" ref="C16:D19" si="4">C42</f>
+        <f t="shared" ref="C16:D19" si="5">C42</f>
         <v>0</v>
       </c>
       <c r="D16" s="188">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E16" s="276"/>
@@ -8395,21 +8395,21 @@
         <v>0</v>
       </c>
       <c r="AV16" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="440"/>
+      <c r="A17" s="442"/>
       <c r="B17" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="309">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D17" s="188">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E17" s="276"/>
@@ -8495,21 +8495,21 @@
         <v>0</v>
       </c>
       <c r="AV17" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:90" ht="37.35" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="440"/>
+      <c r="A18" s="442"/>
       <c r="B18" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="313">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D18" s="279">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E18" s="276"/>
@@ -8595,21 +8595,21 @@
         <v>0</v>
       </c>
       <c r="AV18" s="397">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:90" ht="37.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="440"/>
+      <c r="A19" s="442"/>
       <c r="B19" s="35" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="317">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D19" s="279">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E19" s="290"/>
@@ -8695,12 +8695,12 @@
         <v>0</v>
       </c>
       <c r="AV19" s="409">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BD19" s="425"/>
-      <c r="BE19" s="426"/>
-      <c r="BF19" s="426"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BD19" s="446"/>
+      <c r="BE19" s="447"/>
+      <c r="BF19" s="447"/>
       <c r="BJ19" s="56"/>
       <c r="BK19" s="56"/>
       <c r="BL19" s="56"/>
@@ -8787,7 +8787,7 @@
       <c r="BC20" s="392"/>
     </row>
     <row r="21" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="440" t="s">
+      <c r="A21" s="442" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="68" t="s">
@@ -8833,63 +8833,63 @@
         <v>0</v>
       </c>
       <c r="AN21" s="389">
-        <f t="shared" ref="AN21:BB30" si="5">COUNTIF($E21:$AK21,"*"&amp;AN$66&amp;"*")</f>
+        <f t="shared" ref="AN21:BB30" si="6">COUNTIF($E21:$AK21,"*"&amp;AN$66&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="AO21" s="190">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP21" s="191">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ21" s="390">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR21" s="192">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS21" s="138">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT21" s="190">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU21" s="190">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV21" s="190">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW21" s="191">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX21" s="138">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY21" s="190">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ21" s="193">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA21" s="390">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB21" s="193">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC21" s="193">
@@ -8903,7 +8903,7 @@
       <c r="BI21" s="81"/>
     </row>
     <row r="22" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="440"/>
+      <c r="A22" s="442"/>
       <c r="B22" s="82" t="s">
         <v>28</v>
       </c>
@@ -8943,71 +8943,71 @@
       <c r="AJ22" s="70"/>
       <c r="AK22" s="71"/>
       <c r="AM22" s="72">
-        <f t="shared" ref="AM22:AM65" si="6">D22</f>
+        <f t="shared" ref="AM22:AM65" si="7">D22</f>
         <v>0</v>
       </c>
       <c r="AN22" s="83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AO22" s="84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP22" s="85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ22" s="86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR22" s="87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS22" s="88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT22" s="84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU22" s="87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV22" s="87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW22" s="85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX22" s="88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY22" s="84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ22" s="89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA22" s="86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB22" s="89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC22" s="89">
-        <f t="shared" ref="BC22:BC65" si="7">SUM(AN22:AZ22)</f>
+        <f t="shared" ref="BC22:BC65" si="8">SUM(AN22:AZ22)</f>
         <v>0</v>
       </c>
       <c r="BD22" s="79"/>
@@ -9017,7 +9017,7 @@
       <c r="BI22" s="81"/>
     </row>
     <row r="23" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="440"/>
+      <c r="A23" s="442"/>
       <c r="B23" s="90" t="s">
         <v>29</v>
       </c>
@@ -9057,71 +9057,71 @@
       <c r="AJ23" s="70"/>
       <c r="AK23" s="71"/>
       <c r="AM23" s="72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN23" s="91">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="91">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AO23" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP23" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ23" s="94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR23" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS23" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT23" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU23" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV23" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW23" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX23" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY23" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ23" s="97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA23" s="94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB23" s="97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC23" s="97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD23" s="79"/>
@@ -9131,7 +9131,7 @@
       <c r="BI23" s="81"/>
     </row>
     <row r="24" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="440"/>
+      <c r="A24" s="442"/>
       <c r="B24" s="98" t="s">
         <v>7</v>
       </c>
@@ -9171,71 +9171,71 @@
       <c r="AJ24" s="70"/>
       <c r="AK24" s="71"/>
       <c r="AM24" s="72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="91">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN24" s="91">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AO24" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP24" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ24" s="94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR24" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS24" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT24" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU24" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV24" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW24" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX24" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY24" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ24" s="97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA24" s="94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB24" s="97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC24" s="97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD24" s="79"/>
@@ -9245,7 +9245,7 @@
       <c r="BI24" s="81"/>
     </row>
     <row r="25" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="440"/>
+      <c r="A25" s="442"/>
       <c r="B25" s="98" t="s">
         <v>8</v>
       </c>
@@ -9285,71 +9285,71 @@
       <c r="AJ25" s="70"/>
       <c r="AK25" s="71"/>
       <c r="AM25" s="72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="91">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="91">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AO25" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP25" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ25" s="94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR25" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS25" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT25" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU25" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV25" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW25" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX25" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY25" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ25" s="97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA25" s="94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB25" s="97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC25" s="97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD25" s="79"/>
@@ -9359,7 +9359,7 @@
       <c r="BI25" s="81"/>
     </row>
     <row r="26" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="440"/>
+      <c r="A26" s="442"/>
       <c r="B26" s="99" t="s">
         <v>30</v>
       </c>
@@ -9399,71 +9399,71 @@
       <c r="AJ26" s="70"/>
       <c r="AK26" s="71"/>
       <c r="AM26" s="72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN26" s="91">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="91">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AO26" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP26" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ26" s="94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR26" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS26" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT26" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU26" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV26" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW26" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX26" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY26" s="92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ26" s="97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA26" s="94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB26" s="97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC26" s="97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD26" s="79"/>
@@ -9473,7 +9473,7 @@
       <c r="BI26" s="81"/>
     </row>
     <row r="27" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="440"/>
+      <c r="A27" s="442"/>
       <c r="B27" s="82" t="s">
         <v>30</v>
       </c>
@@ -9513,71 +9513,71 @@
       <c r="AJ27" s="70"/>
       <c r="AK27" s="71"/>
       <c r="AM27" s="72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN27" s="100">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN27" s="100">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AO27" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP27" s="102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ27" s="103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR27" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS27" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT27" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU27" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV27" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW27" s="102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX27" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY27" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ27" s="106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA27" s="103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB27" s="106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC27" s="106">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD27" s="79"/>
@@ -9587,7 +9587,7 @@
       <c r="BI27" s="81"/>
     </row>
     <row r="28" spans="1:90" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="440"/>
+      <c r="A28" s="442"/>
       <c r="B28" s="82" t="s">
         <v>30</v>
       </c>
@@ -9627,71 +9627,71 @@
       <c r="AJ28" s="70"/>
       <c r="AK28" s="71"/>
       <c r="AM28" s="72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN28" s="100">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN28" s="100">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AO28" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP28" s="102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ28" s="103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR28" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS28" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT28" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU28" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV28" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW28" s="102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX28" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY28" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ28" s="106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA28" s="103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB28" s="106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC28" s="106">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD28" s="79"/>
@@ -9701,7 +9701,7 @@
       <c r="BI28" s="81"/>
     </row>
     <row r="29" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="440"/>
+      <c r="A29" s="442"/>
       <c r="B29" s="82" t="s">
         <v>30</v>
       </c>
@@ -9741,71 +9741,71 @@
       <c r="AJ29" s="70"/>
       <c r="AK29" s="71"/>
       <c r="AM29" s="72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN29" s="100">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN29" s="100">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AO29" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP29" s="102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ29" s="103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR29" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT29" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU29" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV29" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW29" s="102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY29" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ29" s="106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA29" s="103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB29" s="106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC29" s="106">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD29" s="79"/>
@@ -9815,7 +9815,7 @@
       <c r="BI29" s="81"/>
     </row>
     <row r="30" spans="1:90" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="440"/>
+      <c r="A30" s="442"/>
       <c r="B30" s="82" t="s">
         <v>30</v>
       </c>
@@ -9855,71 +9855,71 @@
       <c r="AJ30" s="70"/>
       <c r="AK30" s="71"/>
       <c r="AM30" s="72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN30" s="108">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN30" s="108">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AO30" s="109">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP30" s="110">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ30" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR30" s="112">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS30" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT30" s="109">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU30" s="112">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AV30" s="112">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AW30" s="110">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AX30" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AY30" s="109">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AZ30" s="114">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BA30" s="111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB30" s="114">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BC30" s="114">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD30" s="79"/>
@@ -9929,7 +9929,7 @@
       <c r="BI30" s="81"/>
     </row>
     <row r="31" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="439" t="s">
+      <c r="A31" s="441" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="115" t="s">
@@ -9971,71 +9971,71 @@
       <c r="AJ31" s="129"/>
       <c r="AK31" s="130"/>
       <c r="AM31" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN31" s="73">
-        <f t="shared" ref="AN31:BB40" si="8">COUNTIF($E31:$AK31,"*"&amp;AN$66&amp;"*")</f>
+        <f t="shared" ref="AN31:BB40" si="9">COUNTIF($E31:$AK31,"*"&amp;AN$66&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="AO31" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP31" s="77">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="131">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR31" s="74">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS31" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT31" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU31" s="74">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV31" s="74">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW31" s="77">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX31" s="75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY31" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ31" s="78">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA31" s="131">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB31" s="78">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC31" s="78">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP31" s="77">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="131">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR31" s="74">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS31" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT31" s="76">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU31" s="74">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV31" s="74">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW31" s="77">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX31" s="75">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY31" s="76">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ31" s="78">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA31" s="131">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB31" s="78">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC31" s="78">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD31" s="79"/>
@@ -10045,7 +10045,7 @@
       <c r="BI31" s="81"/>
     </row>
     <row r="32" spans="1:90" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="440"/>
+      <c r="A32" s="442"/>
       <c r="B32" s="132" t="s">
         <v>28</v>
       </c>
@@ -10085,71 +10085,71 @@
       <c r="AJ32" s="70"/>
       <c r="AK32" s="71"/>
       <c r="AM32" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN32" s="91">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO32" s="92">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP32" s="93">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="94">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR32" s="95">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS32" s="96">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT32" s="92">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU32" s="95">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV32" s="95">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW32" s="93">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX32" s="96">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY32" s="92">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="97">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA32" s="94">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB32" s="97">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC32" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO32" s="92">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP32" s="93">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ32" s="94">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR32" s="95">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS32" s="96">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT32" s="92">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU32" s="95">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV32" s="95">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW32" s="93">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX32" s="96">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY32" s="92">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ32" s="97">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA32" s="94">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB32" s="97">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC32" s="97">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD32" s="79"/>
@@ -10159,7 +10159,7 @@
       <c r="BI32" s="81"/>
     </row>
     <row r="33" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="440"/>
+      <c r="A33" s="442"/>
       <c r="B33" s="68" t="s">
         <v>29</v>
       </c>
@@ -10199,71 +10199,71 @@
       <c r="AJ33" s="70"/>
       <c r="AK33" s="71"/>
       <c r="AM33" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN33" s="133">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO33" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP33" s="135">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ33" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR33" s="137">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS33" s="138">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT33" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU33" s="137">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV33" s="137">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW33" s="135">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX33" s="138">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY33" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ33" s="139">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA33" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB33" s="139">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC33" s="139">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO33" s="134">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP33" s="135">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ33" s="136">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR33" s="137">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS33" s="138">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT33" s="134">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU33" s="137">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV33" s="137">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW33" s="135">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX33" s="138">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY33" s="134">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ33" s="139">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA33" s="136">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB33" s="139">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC33" s="139">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD33" s="79"/>
@@ -10273,7 +10273,7 @@
       <c r="BI33" s="81"/>
     </row>
     <row r="34" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="440"/>
+      <c r="A34" s="442"/>
       <c r="B34" s="132" t="s">
         <v>32</v>
       </c>
@@ -10313,71 +10313,71 @@
       <c r="AJ34" s="70"/>
       <c r="AK34" s="71"/>
       <c r="AM34" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN34" s="140">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO34" s="141">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP34" s="142">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR34" s="137">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS34" s="138">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT34" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU34" s="137">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV34" s="137">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW34" s="135">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX34" s="138">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY34" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ34" s="139">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA34" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB34" s="139">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC34" s="139">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO34" s="141">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP34" s="142">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="136">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR34" s="137">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS34" s="138">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT34" s="134">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU34" s="137">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV34" s="137">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW34" s="135">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX34" s="138">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY34" s="134">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ34" s="139">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA34" s="136">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB34" s="139">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC34" s="139">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD34" s="79"/>
@@ -10387,7 +10387,7 @@
       <c r="BI34" s="81"/>
     </row>
     <row r="35" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="440"/>
+      <c r="A35" s="442"/>
       <c r="B35" s="143" t="s">
         <v>33</v>
       </c>
@@ -10427,71 +10427,71 @@
       <c r="AJ35" s="70"/>
       <c r="AK35" s="71"/>
       <c r="AM35" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN35" s="140">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO35" s="144">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP35" s="145">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR35" s="146">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS35" s="147">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT35" s="144">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU35" s="146">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV35" s="146">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW35" s="142">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX35" s="147">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY35" s="144">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ35" s="148">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA35" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB35" s="148">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC35" s="148">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO35" s="144">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP35" s="145">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="136">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR35" s="146">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS35" s="147">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT35" s="144">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU35" s="146">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV35" s="146">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW35" s="142">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX35" s="147">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY35" s="144">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ35" s="148">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA35" s="136">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB35" s="148">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC35" s="148">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD35" s="79"/>
@@ -10501,7 +10501,7 @@
       <c r="BI35" s="81"/>
     </row>
     <row r="36" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="440"/>
+      <c r="A36" s="442"/>
       <c r="B36" s="149" t="s">
         <v>30</v>
       </c>
@@ -10541,71 +10541,71 @@
       <c r="AJ36" s="70"/>
       <c r="AK36" s="71"/>
       <c r="AM36" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN36" s="140">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO36" s="150">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP36" s="151">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR36" s="152">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS36" s="147">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT36" s="150">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU36" s="152">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV36" s="152">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW36" s="151">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX36" s="147">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY36" s="150">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ36" s="153">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA36" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB36" s="153">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC36" s="153">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO36" s="150">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP36" s="151">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="136">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR36" s="152">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS36" s="147">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT36" s="150">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU36" s="152">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV36" s="152">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW36" s="151">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX36" s="147">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY36" s="150">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ36" s="153">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA36" s="136">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB36" s="153">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC36" s="153">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD36" s="79"/>
@@ -10615,7 +10615,7 @@
       <c r="BI36" s="81"/>
     </row>
     <row r="37" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="440"/>
+      <c r="A37" s="442"/>
       <c r="B37" s="82" t="s">
         <v>30</v>
       </c>
@@ -10655,71 +10655,71 @@
       <c r="AJ37" s="70"/>
       <c r="AK37" s="71"/>
       <c r="AM37" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN37" s="91">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO37" s="92">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP37" s="93">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="94">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR37" s="95">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS37" s="96">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT37" s="92">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU37" s="95">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV37" s="95">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW37" s="93">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX37" s="96">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY37" s="92">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ37" s="97">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA37" s="94">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB37" s="97">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC37" s="97">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO37" s="92">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP37" s="93">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="94">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR37" s="95">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS37" s="96">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT37" s="92">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU37" s="95">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV37" s="95">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW37" s="93">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX37" s="96">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY37" s="92">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ37" s="97">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA37" s="94">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB37" s="97">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC37" s="97">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD37" s="79"/>
@@ -10729,7 +10729,7 @@
       <c r="BI37" s="81"/>
     </row>
     <row r="38" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="440"/>
+      <c r="A38" s="442"/>
       <c r="B38" s="154" t="s">
         <v>30</v>
       </c>
@@ -10769,71 +10769,71 @@
       <c r="AJ38" s="156"/>
       <c r="AK38" s="157"/>
       <c r="AM38" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN38" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO38" s="159">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP38" s="160">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="161">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR38" s="162">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS38" s="163">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT38" s="159">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU38" s="162">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV38" s="162">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW38" s="160">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX38" s="163">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY38" s="159">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ38" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA38" s="161">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB38" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC38" s="164">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO38" s="159">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP38" s="160">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="161">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR38" s="162">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS38" s="163">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT38" s="159">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU38" s="162">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV38" s="162">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW38" s="160">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX38" s="163">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY38" s="159">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ38" s="164">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA38" s="161">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB38" s="164">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC38" s="164">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD38" s="79"/>
@@ -10843,7 +10843,7 @@
       <c r="BI38" s="81"/>
     </row>
     <row r="39" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="440"/>
+      <c r="A39" s="442"/>
       <c r="B39" s="154" t="s">
         <v>30</v>
       </c>
@@ -10883,71 +10883,71 @@
       <c r="AJ39" s="156"/>
       <c r="AK39" s="157"/>
       <c r="AM39" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN39" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO39" s="159">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP39" s="160">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="161">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR39" s="162">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS39" s="163">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT39" s="159">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU39" s="162">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV39" s="162">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW39" s="160">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX39" s="163">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY39" s="159">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA39" s="161">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB39" s="164">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC39" s="164">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO39" s="159">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP39" s="160">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="161">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR39" s="162">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS39" s="163">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT39" s="159">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU39" s="162">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV39" s="162">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW39" s="160">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX39" s="163">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY39" s="159">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ39" s="164">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA39" s="161">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB39" s="164">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC39" s="164">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD39" s="79"/>
@@ -10957,7 +10957,7 @@
       <c r="BI39" s="81"/>
     </row>
     <row r="40" spans="1:61" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="441"/>
+      <c r="A40" s="443"/>
       <c r="B40" s="165" t="s">
         <v>30</v>
       </c>
@@ -10997,71 +10997,71 @@
       <c r="AJ40" s="167"/>
       <c r="AK40" s="168"/>
       <c r="AM40" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN40" s="108">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO40" s="109">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP40" s="110">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ40" s="111">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR40" s="112">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS40" s="113">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT40" s="109">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU40" s="112">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV40" s="112">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW40" s="110">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX40" s="113">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY40" s="109">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA40" s="111">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BB40" s="114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BC40" s="114">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AO40" s="109">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AP40" s="110">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AQ40" s="111">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR40" s="112">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS40" s="113">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT40" s="109">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU40" s="112">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV40" s="112">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW40" s="110">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AX40" s="113">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY40" s="109">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ40" s="114">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA40" s="111">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BB40" s="114">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BC40" s="114">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BD40" s="79"/>
@@ -11071,7 +11071,7 @@
       <c r="BI40" s="81"/>
     </row>
     <row r="41" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="439" t="s">
+      <c r="A41" s="441" t="s">
         <v>34</v>
       </c>
       <c r="B41" s="169" t="s">
@@ -11113,71 +11113,71 @@
       <c r="AJ41" s="129"/>
       <c r="AK41" s="130"/>
       <c r="AM41" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN41" s="140">
-        <f t="shared" ref="AN41:BB55" si="9">COUNTIF($E41:$AK41,"*"&amp;AN$66&amp;"*")</f>
+        <f t="shared" ref="AN41:BB55" si="10">COUNTIF($E41:$AK41,"*"&amp;AN$66&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="AO41" s="150">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP41" s="151">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ41" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR41" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS41" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT41" s="150">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU41" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV41" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW41" s="151">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX41" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY41" s="150">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ41" s="153">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA41" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB41" s="153">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC41" s="153">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD41" s="79"/>
@@ -11187,7 +11187,7 @@
       <c r="BI41" s="81"/>
     </row>
     <row r="42" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="440"/>
+      <c r="A42" s="442"/>
       <c r="B42" s="170" t="s">
         <v>28</v>
       </c>
@@ -11227,71 +11227,71 @@
       <c r="AJ42" s="172"/>
       <c r="AK42" s="173"/>
       <c r="AM42" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN42" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO42" s="175">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP42" s="176">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ42" s="177">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR42" s="178">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS42" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT42" s="175">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU42" s="178">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV42" s="178">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW42" s="176">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX42" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY42" s="175">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ42" s="180">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA42" s="177">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB42" s="180">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC42" s="180">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD42" s="79"/>
@@ -11301,7 +11301,7 @@
       <c r="BI42" s="81"/>
     </row>
     <row r="43" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="440"/>
+      <c r="A43" s="442"/>
       <c r="B43" s="181" t="s">
         <v>29</v>
       </c>
@@ -11341,71 +11341,71 @@
       <c r="AJ43" s="172"/>
       <c r="AK43" s="173"/>
       <c r="AM43" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN43" s="140">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO43" s="150">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP43" s="151">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ43" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR43" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS43" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT43" s="150">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU43" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV43" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW43" s="151">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX43" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY43" s="150">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ43" s="153">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA43" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB43" s="153">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC43" s="153">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD43" s="79"/>
@@ -11415,7 +11415,7 @@
       <c r="BI43" s="81"/>
     </row>
     <row r="44" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="440"/>
+      <c r="A44" s="442"/>
       <c r="B44" s="182" t="s">
         <v>32</v>
       </c>
@@ -11455,71 +11455,71 @@
       <c r="AJ44" s="172"/>
       <c r="AK44" s="173"/>
       <c r="AM44" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN44" s="140">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO44" s="183">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP44" s="184">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ44" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR44" s="185">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS44" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT44" s="183">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU44" s="185">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV44" s="185">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW44" s="184">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX44" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY44" s="183">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ44" s="186">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA44" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB44" s="186">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC44" s="186">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD44" s="79"/>
@@ -11529,7 +11529,7 @@
       <c r="BI44" s="81"/>
     </row>
     <row r="45" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="440"/>
+      <c r="A45" s="442"/>
       <c r="B45" s="187" t="s">
         <v>33</v>
       </c>
@@ -11569,71 +11569,71 @@
       <c r="AJ45" s="172"/>
       <c r="AK45" s="173"/>
       <c r="AM45" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN45" s="140">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO45" s="190">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP45" s="191">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ45" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR45" s="192">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS45" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT45" s="190">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU45" s="192">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV45" s="192">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW45" s="191">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX45" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY45" s="190">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ45" s="193">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA45" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB45" s="193">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC45" s="193">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD45" s="79"/>
@@ -11643,7 +11643,7 @@
       <c r="BI45" s="81"/>
     </row>
     <row r="46" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="440"/>
+      <c r="A46" s="442"/>
       <c r="B46" s="194" t="s">
         <v>30</v>
       </c>
@@ -11683,71 +11683,71 @@
       <c r="AJ46" s="172"/>
       <c r="AK46" s="173"/>
       <c r="AM46" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN46" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO46" s="175">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP46" s="176">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ46" s="177">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR46" s="178">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS46" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT46" s="175">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU46" s="178">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV46" s="178">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW46" s="176">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX46" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY46" s="175">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ46" s="180">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA46" s="177">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB46" s="180">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC46" s="180">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD46" s="79"/>
@@ -11757,7 +11757,7 @@
       <c r="BI46" s="81"/>
     </row>
     <row r="47" spans="1:61" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="440"/>
+      <c r="A47" s="442"/>
       <c r="B47" s="195" t="s">
         <v>30</v>
       </c>
@@ -11797,71 +11797,71 @@
       <c r="AJ47" s="198"/>
       <c r="AK47" s="199"/>
       <c r="AM47" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN47" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO47" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP47" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ47" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR47" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS47" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT47" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU47" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV47" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW47" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX47" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY47" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ47" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA47" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB47" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC47" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD47" s="79"/>
@@ -11871,7 +11871,7 @@
       <c r="BI47" s="81"/>
     </row>
     <row r="48" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="440"/>
+      <c r="A48" s="442"/>
       <c r="B48" s="195" t="s">
         <v>30</v>
       </c>
@@ -11911,71 +11911,71 @@
       <c r="AJ48" s="198"/>
       <c r="AK48" s="199"/>
       <c r="AM48" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN48" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO48" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP48" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ48" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR48" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS48" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT48" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU48" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV48" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW48" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX48" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY48" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ48" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA48" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB48" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC48" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD48" s="79"/>
@@ -11985,7 +11985,7 @@
       <c r="BI48" s="81"/>
     </row>
     <row r="49" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="440"/>
+      <c r="A49" s="442"/>
       <c r="B49" s="195" t="s">
         <v>30</v>
       </c>
@@ -12025,71 +12025,71 @@
       <c r="AJ49" s="198"/>
       <c r="AK49" s="199"/>
       <c r="AM49" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN49" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO49" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP49" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ49" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR49" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS49" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT49" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU49" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV49" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW49" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX49" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY49" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ49" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA49" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB49" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC49" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD49" s="79"/>
@@ -12099,7 +12099,7 @@
       <c r="BI49" s="81"/>
     </row>
     <row r="50" spans="1:61" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="441"/>
+      <c r="A50" s="443"/>
       <c r="B50" s="205" t="s">
         <v>30</v>
       </c>
@@ -12139,71 +12139,71 @@
       <c r="AJ50" s="211"/>
       <c r="AK50" s="212"/>
       <c r="AM50" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN50" s="213">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO50" s="214">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP50" s="215">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ50" s="216">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR50" s="217">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS50" s="218">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT50" s="214">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU50" s="217">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV50" s="217">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW50" s="215">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX50" s="218">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY50" s="214">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ50" s="219">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA50" s="216">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB50" s="219">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC50" s="219">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD50" s="79"/>
@@ -12213,7 +12213,7 @@
       <c r="BI50" s="81"/>
     </row>
     <row r="51" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="439" t="s">
+      <c r="A51" s="441" t="s">
         <v>35</v>
       </c>
       <c r="B51" s="220" t="s">
@@ -12255,71 +12255,71 @@
       <c r="AJ51" s="129"/>
       <c r="AK51" s="130"/>
       <c r="AM51" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN51" s="140">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO51" s="190">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP51" s="191">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ51" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR51" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS51" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT51" s="150">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU51" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV51" s="152">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW51" s="191">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX51" s="147">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY51" s="150">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ51" s="193">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA51" s="136">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB51" s="193">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC51" s="193">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD51" s="79"/>
@@ -12329,7 +12329,7 @@
       <c r="BI51" s="81"/>
     </row>
     <row r="52" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="440"/>
+      <c r="A52" s="442"/>
       <c r="B52" s="230" t="s">
         <v>36</v>
       </c>
@@ -12369,71 +12369,71 @@
       <c r="AJ52" s="198"/>
       <c r="AK52" s="199"/>
       <c r="AM52" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN52" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO52" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP52" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ52" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR52" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS52" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT52" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU52" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV52" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW52" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX52" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY52" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ52" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA52" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB52" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC52" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD52" s="79"/>
@@ -12443,7 +12443,7 @@
       <c r="BI52" s="81"/>
     </row>
     <row r="53" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="440"/>
+      <c r="A53" s="442"/>
       <c r="B53" s="230" t="s">
         <v>36</v>
       </c>
@@ -12483,71 +12483,71 @@
       <c r="AJ53" s="198"/>
       <c r="AK53" s="199"/>
       <c r="AM53" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN53" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO53" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP53" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ53" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR53" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS53" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT53" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU53" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV53" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW53" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX53" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY53" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ53" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA53" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB53" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC53" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD53" s="79"/>
@@ -12557,7 +12557,7 @@
       <c r="BI53" s="81"/>
     </row>
     <row r="54" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="440"/>
+      <c r="A54" s="442"/>
       <c r="B54" s="230" t="s">
         <v>36</v>
       </c>
@@ -12597,71 +12597,71 @@
       <c r="AJ54" s="198"/>
       <c r="AK54" s="199"/>
       <c r="AM54" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN54" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO54" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP54" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ54" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR54" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS54" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT54" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU54" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV54" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW54" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX54" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY54" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ54" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA54" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB54" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC54" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD54" s="79"/>
@@ -12671,7 +12671,7 @@
       <c r="BI54" s="81"/>
     </row>
     <row r="55" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="440"/>
+      <c r="A55" s="442"/>
       <c r="B55" s="230" t="s">
         <v>36</v>
       </c>
@@ -12711,71 +12711,71 @@
       <c r="AJ55" s="198"/>
       <c r="AK55" s="199"/>
       <c r="AM55" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN55" s="174">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO55" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP55" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ55" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR55" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS55" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT55" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU55" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV55" s="203">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW55" s="201">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AX55" s="179">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AY55" s="200">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AZ55" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BA55" s="202">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BB55" s="204">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BC55" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD55" s="79"/>
@@ -12785,7 +12785,7 @@
       <c r="BI55" s="81"/>
     </row>
     <row r="56" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="440"/>
+      <c r="A56" s="442"/>
       <c r="B56" s="230" t="s">
         <v>36</v>
       </c>
@@ -12825,59 +12825,59 @@
       <c r="AJ56" s="198"/>
       <c r="AK56" s="199"/>
       <c r="AM56" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN56" s="174">
-        <f t="shared" ref="AN56:AZ65" si="10">COUNTIF($E56:$AK56,"*"&amp;AN$66&amp;"*")</f>
+        <f t="shared" ref="AN56:AZ65" si="11">COUNTIF($E56:$AK56,"*"&amp;AN$66&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="AO56" s="200">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP56" s="201">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ56" s="202">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR56" s="203">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS56" s="179">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT56" s="200">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU56" s="203">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV56" s="203">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW56" s="201">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX56" s="179">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY56" s="200">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ56" s="204">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA56" s="202">
@@ -12889,7 +12889,7 @@
         <v>0</v>
       </c>
       <c r="BC56" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD56" s="79"/>
@@ -12899,7 +12899,7 @@
       <c r="BI56" s="81"/>
     </row>
     <row r="57" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="440"/>
+      <c r="A57" s="442"/>
       <c r="B57" s="230" t="s">
         <v>36</v>
       </c>
@@ -12939,71 +12939,71 @@
       <c r="AJ57" s="198"/>
       <c r="AK57" s="199"/>
       <c r="AM57" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN57" s="174">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO57" s="200">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP57" s="201">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ57" s="202">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR57" s="203">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS57" s="179">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT57" s="200">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU57" s="203">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV57" s="203">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW57" s="201">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX57" s="179">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY57" s="200">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ57" s="204">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA57" s="202">
-        <f t="shared" ref="BA57:BB65" si="11">COUNTIF($E57:$AK57,"*"&amp;BA$66&amp;"*")</f>
+        <f t="shared" ref="BA57:BB65" si="12">COUNTIF($E57:$AK57,"*"&amp;BA$66&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="BB57" s="204">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC57" s="204">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD57" s="79"/>
@@ -13013,7 +13013,7 @@
       <c r="BI57" s="81"/>
     </row>
     <row r="58" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="440"/>
+      <c r="A58" s="442"/>
       <c r="B58" s="230" t="s">
         <v>36</v>
       </c>
@@ -13053,71 +13053,71 @@
       <c r="AJ58" s="198"/>
       <c r="AK58" s="199"/>
       <c r="AM58" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN58" s="231">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO58" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP58" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ58" s="234">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR58" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS58" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT58" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU58" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV58" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW58" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX58" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY58" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ58" s="237">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA58" s="234">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB58" s="237">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC58" s="237">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD58" s="79"/>
@@ -13127,7 +13127,7 @@
       <c r="BI58" s="81"/>
     </row>
     <row r="59" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="440"/>
+      <c r="A59" s="442"/>
       <c r="B59" s="230" t="s">
         <v>36</v>
       </c>
@@ -13167,71 +13167,71 @@
       <c r="AJ59" s="198"/>
       <c r="AK59" s="199"/>
       <c r="AM59" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN59" s="231">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO59" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP59" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ59" s="234">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR59" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS59" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT59" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU59" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV59" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW59" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX59" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY59" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ59" s="237">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA59" s="234">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB59" s="237">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC59" s="237">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD59" s="79"/>
@@ -13241,7 +13241,7 @@
       <c r="BI59" s="81"/>
     </row>
     <row r="60" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="440"/>
+      <c r="A60" s="442"/>
       <c r="B60" s="230" t="s">
         <v>36</v>
       </c>
@@ -13281,71 +13281,71 @@
       <c r="AJ60" s="198"/>
       <c r="AK60" s="199"/>
       <c r="AM60" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN60" s="231">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO60" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP60" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ60" s="234">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR60" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS60" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT60" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU60" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV60" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW60" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX60" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY60" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ60" s="237">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA60" s="234">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB60" s="237">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC60" s="237">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD60" s="79"/>
@@ -13355,7 +13355,7 @@
       <c r="BI60" s="81"/>
     </row>
     <row r="61" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="440"/>
+      <c r="A61" s="442"/>
       <c r="B61" s="230" t="s">
         <v>36</v>
       </c>
@@ -13395,71 +13395,71 @@
       <c r="AJ61" s="156"/>
       <c r="AK61" s="157"/>
       <c r="AM61" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN61" s="231">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO61" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP61" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ61" s="234">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR61" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS61" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT61" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU61" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV61" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW61" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX61" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY61" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ61" s="237">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA61" s="234">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB61" s="237">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC61" s="237">
-        <f t="shared" ref="BC61:BC62" si="12">SUM(AN61:AZ61)</f>
+        <f t="shared" ref="BC61:BC62" si="13">SUM(AN61:AZ61)</f>
         <v>0</v>
       </c>
       <c r="BD61" s="79"/>
@@ -13469,7 +13469,7 @@
       <c r="BI61" s="81"/>
     </row>
     <row r="62" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="440"/>
+      <c r="A62" s="442"/>
       <c r="B62" s="230" t="s">
         <v>36</v>
       </c>
@@ -13509,71 +13509,71 @@
       <c r="AJ62" s="156"/>
       <c r="AK62" s="157"/>
       <c r="AM62" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN62" s="231">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO62" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP62" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ62" s="234">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR62" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS62" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT62" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU62" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV62" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW62" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX62" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY62" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ62" s="237">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA62" s="234">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB62" s="237">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC62" s="237">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD62" s="79"/>
@@ -13583,7 +13583,7 @@
       <c r="BI62" s="81"/>
     </row>
     <row r="63" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="440"/>
+      <c r="A63" s="442"/>
       <c r="B63" s="230" t="s">
         <v>36</v>
       </c>
@@ -13623,71 +13623,71 @@
       <c r="AJ63" s="198"/>
       <c r="AK63" s="199"/>
       <c r="AM63" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN63" s="231">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO63" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP63" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ63" s="234">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR63" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS63" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT63" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU63" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV63" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW63" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX63" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY63" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ63" s="237">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA63" s="234">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB63" s="237">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC63" s="237">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD63" s="79"/>
@@ -13697,7 +13697,7 @@
       <c r="BI63" s="81"/>
     </row>
     <row r="64" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="440"/>
+      <c r="A64" s="442"/>
       <c r="B64" s="230" t="s">
         <v>36</v>
       </c>
@@ -13737,71 +13737,71 @@
       <c r="AJ64" s="198"/>
       <c r="AK64" s="199"/>
       <c r="AM64" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN64" s="231">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO64" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP64" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ64" s="234">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR64" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS64" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT64" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU64" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV64" s="235">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW64" s="233">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX64" s="236">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY64" s="232">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ64" s="237">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA64" s="234">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB64" s="237">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC64" s="237">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD64" s="79"/>
@@ -13811,7 +13811,7 @@
       <c r="BI64" s="81"/>
     </row>
     <row r="65" spans="1:90" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="441"/>
+      <c r="A65" s="443"/>
       <c r="B65" s="238" t="s">
         <v>36</v>
       </c>
@@ -13851,71 +13851,71 @@
       <c r="AJ65" s="211"/>
       <c r="AK65" s="212"/>
       <c r="AM65" s="72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN65" s="239">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO65" s="240">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP65" s="241">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ65" s="242">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR65" s="243">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS65" s="244">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT65" s="240">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU65" s="243">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AV65" s="243">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AW65" s="241">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AX65" s="244">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AY65" s="240">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ65" s="245">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA65" s="242">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB65" s="245">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BC65" s="245">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BD65" s="79"/>
@@ -13925,45 +13925,45 @@
       <c r="BI65" s="81"/>
     </row>
     <row r="66" spans="1:90" s="246" customFormat="1" ht="52.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="427"/>
-      <c r="B66" s="428"/>
-      <c r="C66" s="428"/>
-      <c r="D66" s="429"/>
-      <c r="E66" s="430"/>
-      <c r="F66" s="431"/>
-      <c r="G66" s="431"/>
-      <c r="H66" s="431"/>
-      <c r="I66" s="431"/>
-      <c r="J66" s="432"/>
-      <c r="K66" s="433"/>
-      <c r="L66" s="434"/>
-      <c r="M66" s="434"/>
-      <c r="N66" s="434"/>
-      <c r="O66" s="434"/>
-      <c r="P66" s="435"/>
-      <c r="Q66" s="433"/>
-      <c r="R66" s="434"/>
-      <c r="S66" s="434"/>
-      <c r="T66" s="434"/>
-      <c r="U66" s="435"/>
-      <c r="V66" s="433"/>
-      <c r="W66" s="434"/>
-      <c r="X66" s="434"/>
-      <c r="Y66" s="434"/>
-      <c r="Z66" s="434"/>
-      <c r="AA66" s="435"/>
-      <c r="AB66" s="433"/>
-      <c r="AC66" s="434"/>
-      <c r="AD66" s="434"/>
-      <c r="AE66" s="434"/>
-      <c r="AF66" s="434"/>
-      <c r="AG66" s="435"/>
-      <c r="AH66" s="436" t="e">
+      <c r="A66" s="450"/>
+      <c r="B66" s="451"/>
+      <c r="C66" s="451"/>
+      <c r="D66" s="452"/>
+      <c r="E66" s="453"/>
+      <c r="F66" s="454"/>
+      <c r="G66" s="454"/>
+      <c r="H66" s="454"/>
+      <c r="I66" s="454"/>
+      <c r="J66" s="455"/>
+      <c r="K66" s="456"/>
+      <c r="L66" s="457"/>
+      <c r="M66" s="457"/>
+      <c r="N66" s="457"/>
+      <c r="O66" s="457"/>
+      <c r="P66" s="458"/>
+      <c r="Q66" s="456"/>
+      <c r="R66" s="457"/>
+      <c r="S66" s="457"/>
+      <c r="T66" s="457"/>
+      <c r="U66" s="458"/>
+      <c r="V66" s="456"/>
+      <c r="W66" s="457"/>
+      <c r="X66" s="457"/>
+      <c r="Y66" s="457"/>
+      <c r="Z66" s="457"/>
+      <c r="AA66" s="458"/>
+      <c r="AB66" s="456"/>
+      <c r="AC66" s="457"/>
+      <c r="AD66" s="457"/>
+      <c r="AE66" s="457"/>
+      <c r="AF66" s="457"/>
+      <c r="AG66" s="458"/>
+      <c r="AH66" s="459" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AI66" s="437"/>
-      <c r="AJ66" s="437"/>
-      <c r="AK66" s="438"/>
+      <c r="AI66" s="460"/>
+      <c r="AJ66" s="460"/>
+      <c r="AK66" s="461"/>
       <c r="AN66" s="410" t="s">
         <v>11</v>
       </c>
@@ -14051,2762 +14051,2762 @@
       </c>
     </row>
     <row r="77" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C77" s="423" t="s">
+      <c r="C77" s="448" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="424"/>
+      <c r="D77" s="449"/>
       <c r="E77" s="1">
         <f>COUNTIF(E$21:E$65,"*"&amp;$C77&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="F77" s="1">
-        <f t="shared" ref="F77:AK84" si="13">COUNTIF(F$21:F$65,"*"&amp;$C77&amp;"*")</f>
+        <f t="shared" ref="F77:AK84" si="14">COUNTIF(F$21:F$65,"*"&amp;$C77&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AE77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C78" s="423" t="s">
+      <c r="C78" s="448" t="s">
         <v>49</v>
       </c>
-      <c r="D78" s="424"/>
+      <c r="D78" s="449"/>
       <c r="E78" s="1">
-        <f t="shared" ref="E78:T96" si="14">COUNTIF(E$21:E$65,"*"&amp;$C78&amp;"*")</f>
+        <f t="shared" ref="E78:T96" si="15">COUNTIF(E$21:E$65,"*"&amp;$C78&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="F78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AE78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C79" s="423" t="s">
+      <c r="C79" s="448" t="s">
         <v>50</v>
       </c>
-      <c r="D79" s="424"/>
+      <c r="D79" s="449"/>
       <c r="E79" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F79" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="G79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AE79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:90" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C80" s="423" t="s">
+      <c r="C80" s="448" t="s">
         <v>51</v>
       </c>
-      <c r="D80" s="424"/>
+      <c r="D80" s="449"/>
       <c r="E80" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F80" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="G80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AE80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C81" s="423" t="s">
+      <c r="C81" s="448" t="s">
         <v>17</v>
       </c>
-      <c r="D81" s="424"/>
+      <c r="D81" s="449"/>
       <c r="E81" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F81" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="G81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AE81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C82" s="423" t="s">
+      <c r="C82" s="448" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="424"/>
+      <c r="D82" s="449"/>
       <c r="E82" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F82" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="G82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AE82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C83" s="423" t="s">
+      <c r="C83" s="448" t="s">
         <v>52</v>
       </c>
-      <c r="D83" s="424"/>
+      <c r="D83" s="449"/>
       <c r="E83" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F83" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="G83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AE83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C84" s="423" t="s">
+      <c r="C84" s="448" t="s">
         <v>22</v>
       </c>
-      <c r="D84" s="424"/>
+      <c r="D84" s="449"/>
       <c r="E84" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F84" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="G84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Q84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="R84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="V84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AD84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AE84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK84" s="1">
-        <f t="shared" ref="AK84" si="15">COUNTIF(AK$21:AK$65,"*"&amp;$C84&amp;"*")</f>
+        <f t="shared" ref="AK84" si="16">COUNTIF(AK$21:AK$65,"*"&amp;$C84&amp;"*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C85" s="423" t="s">
+      <c r="C85" s="448" t="s">
         <v>23</v>
       </c>
-      <c r="D85" s="424"/>
+      <c r="D85" s="449"/>
       <c r="E85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U85" s="1">
-        <f t="shared" ref="U85:AK96" si="16">COUNTIF(U$21:U$65,"*"&amp;$C85&amp;"*")</f>
+        <f t="shared" ref="U85:AK96" si="17">COUNTIF(U$21:U$65,"*"&amp;$C85&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="V85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK85" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C86" s="423" t="s">
+      <c r="C86" s="448" t="s">
         <v>53</v>
       </c>
-      <c r="D86" s="424"/>
+      <c r="D86" s="449"/>
       <c r="E86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C87" s="423" t="s">
+      <c r="C87" s="448" t="s">
         <v>54</v>
       </c>
-      <c r="D87" s="424"/>
+      <c r="D87" s="449"/>
       <c r="E87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK87" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C88" s="423" t="s">
+      <c r="C88" s="448" t="s">
         <v>55</v>
       </c>
-      <c r="D88" s="424"/>
+      <c r="D88" s="449"/>
       <c r="E88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK88" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C89" s="423" t="s">
+      <c r="C89" s="448" t="s">
         <v>56</v>
       </c>
-      <c r="D89" s="424"/>
+      <c r="D89" s="449"/>
       <c r="E89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C90" s="423" t="s">
+      <c r="C90" s="448" t="s">
         <v>57</v>
       </c>
-      <c r="D90" s="424"/>
+      <c r="D90" s="449"/>
       <c r="E90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C91" s="423" t="s">
+      <c r="C91" s="448" t="s">
         <v>58</v>
       </c>
-      <c r="D91" s="424"/>
+      <c r="D91" s="449"/>
       <c r="E91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C92" s="423">
-        <v>0</v>
-      </c>
-      <c r="D92" s="424"/>
+      <c r="C92" s="448">
+        <v>0</v>
+      </c>
+      <c r="D92" s="449"/>
       <c r="E92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C93" s="423">
-        <v>0</v>
-      </c>
-      <c r="D93" s="424"/>
+      <c r="C93" s="448">
+        <v>0</v>
+      </c>
+      <c r="D93" s="449"/>
       <c r="E93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C94" s="423">
-        <v>0</v>
-      </c>
-      <c r="D94" s="424"/>
+      <c r="C94" s="448">
+        <v>0</v>
+      </c>
+      <c r="D94" s="449"/>
       <c r="E94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK94" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C95" s="423">
-        <v>0</v>
-      </c>
-      <c r="D95" s="424"/>
+      <c r="C95" s="448">
+        <v>0</v>
+      </c>
+      <c r="D95" s="449"/>
       <c r="E95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK95" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C96" s="423">
-        <v>0</v>
-      </c>
-      <c r="D96" s="424"/>
+      <c r="C96" s="448">
+        <v>0</v>
+      </c>
+      <c r="D96" s="449"/>
       <c r="E96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Q96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK96" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -25108,26 +25108,30 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="60">
-    <mergeCell ref="AB1:AE2"/>
-    <mergeCell ref="AF1:AG2"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="K3:P3"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="V3:AA3"/>
-    <mergeCell ref="AB3:AG3"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="A41:A50"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AU3:AU4"/>
+    <mergeCell ref="AV3:AV4"/>
+    <mergeCell ref="AR3:AR4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AP3:AP4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="AS3:AS4"/>
+    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C87:D87"/>
     <mergeCell ref="BD19:BF19"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A66:D66"/>
@@ -25144,30 +25148,26 @@
     <mergeCell ref="A51:A65"/>
     <mergeCell ref="A21:A30"/>
     <mergeCell ref="A31:A40"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="AU3:AU4"/>
-    <mergeCell ref="AV3:AV4"/>
-    <mergeCell ref="AR3:AR4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AS3:AS4"/>
-    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="A41:A50"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AB1:AE2"/>
+    <mergeCell ref="AF1:AG2"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:X2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="AA1:AA2"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C5:D19">
